--- a/output/2026-09-01/enriched_analysis.xlsx
+++ b/output/2026-09-01/enriched_analysis.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gandhar Oil Refinery (India) Limited</t>
+          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -640,13 +640,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>257.72</v>
+        <v>261.8</v>
       </c>
       <c r="J2" t="n">
         <v>158.6</v>
       </c>
       <c r="K2" t="n">
-        <v>62.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L2" t="n">
         <v>64.63</v>
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="Q2" t="n">
-        <v>2518</v>
+        <v>2561</v>
       </c>
       <c r="R2" t="n">
-        <v>8.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>36</v>
@@ -696,13 +696,13 @@
         <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>224.61</v>
+        <v>226.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>164.4</v>
+        <v>165.06</v>
       </c>
       <c r="AC2" t="n">
-        <v>83</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="3">
@@ -737,13 +737,13 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>90.58</v>
+        <v>90.44</v>
       </c>
       <c r="J3" t="n">
         <v>55.78</v>
       </c>
       <c r="K3" t="n">
-        <v>62.4</v>
+        <v>62.1</v>
       </c>
       <c r="L3" t="n">
         <v>67.45999999999999</v>
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.656</v>
+        <v>0.652</v>
       </c>
       <c r="Q3" t="n">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="R3" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="S3" t="n">
         <v>19</v>
@@ -793,13 +793,13 @@
         <v>15.38</v>
       </c>
       <c r="AA3" t="n">
-        <v>74.25</v>
+        <v>74.77</v>
       </c>
       <c r="AB3" t="n">
-        <v>56.94</v>
+        <v>57.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>74.7</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -834,13 +834,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1989.3</v>
+        <v>1911.3</v>
       </c>
       <c r="J4" t="n">
         <v>920.51</v>
       </c>
       <c r="K4" t="n">
-        <v>116.1</v>
+        <v>107.6</v>
       </c>
       <c r="L4" t="n">
         <v>73.16</v>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="Q4" t="n">
-        <v>1990</v>
+        <v>1912</v>
       </c>
       <c r="R4" t="n">
-        <v>51.2</v>
+        <v>49.2</v>
       </c>
       <c r="S4" t="n">
         <v>35</v>
@@ -890,13 +890,13 @@
         <v>16.19</v>
       </c>
       <c r="AA4" t="n">
-        <v>1528.36</v>
+        <v>1542.98</v>
       </c>
       <c r="AB4" t="n">
-        <v>1115.97</v>
+        <v>1121.56</v>
       </c>
       <c r="AC4" t="n">
-        <v>117.3</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -931,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>834.9</v>
+        <v>843.85</v>
       </c>
       <c r="J5" t="n">
         <v>745.6900000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>13.2</v>
       </c>
       <c r="L5" t="n">
         <v>69.61</v>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="Q5" t="n">
-        <v>16400</v>
+        <v>16568</v>
       </c>
       <c r="R5" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="S5" t="n">
         <v>16</v>
@@ -987,13 +987,13 @@
         <v>19</v>
       </c>
       <c r="AA5" t="n">
-        <v>818.14</v>
+        <v>819.41</v>
       </c>
       <c r="AB5" t="n">
-        <v>791.91</v>
+        <v>791.49</v>
       </c>
       <c r="AC5" t="n">
-        <v>11.2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -1028,13 +1028,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>250.68</v>
+        <v>263.2</v>
       </c>
       <c r="J6" t="n">
         <v>217.8</v>
       </c>
       <c r="K6" t="n">
-        <v>15.1</v>
+        <v>20.8</v>
       </c>
       <c r="L6" t="n">
         <v>71.75</v>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.075</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>1099</v>
+        <v>1154</v>
       </c>
       <c r="R6" t="n">
-        <v>14.8</v>
+        <v>15.6</v>
       </c>
       <c r="S6" t="n">
         <v>55</v>
@@ -1084,28 +1084,28 @@
         <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>214.11</v>
+        <v>214.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>181.01</v>
+        <v>181.32</v>
       </c>
       <c r="AC6" t="n">
-        <v>60.4</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>THANGAMAIYL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1113,96 +1113,96 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>70.63</v>
+        <v>5311.5</v>
       </c>
       <c r="J7" t="n">
-        <v>70.34999999999999</v>
+        <v>5198.76</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="L7" t="n">
-        <v>72.56999999999999</v>
+        <v>67.16</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>7.21</v>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.5</v>
+        <v>0.044</v>
       </c>
       <c r="Q7" t="n">
-        <v>208</v>
+        <v>16512</v>
       </c>
       <c r="R7" t="n">
-        <v>8.83</v>
+        <v>42</v>
       </c>
       <c r="S7" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="T7" t="n">
-        <v>27.97</v>
+        <v>145</v>
       </c>
       <c r="U7" t="n">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="V7" t="n">
-        <v>2.73</v>
+        <v>27.38</v>
       </c>
       <c r="W7" t="n">
-        <v>13.7</v>
+        <v>25.5</v>
       </c>
       <c r="X7" t="n">
-        <v>1.86</v>
+        <v>0.64</v>
       </c>
       <c r="Y7" t="b">
         <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.140000000000001</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>56</v>
+        <v>5877.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>51.38</v>
+        <v>4295.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>56.8</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -1222,69 +1222,69 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>5412</v>
+        <v>70.09</v>
       </c>
       <c r="J8" t="n">
-        <v>5187.29</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>-0.4</v>
       </c>
       <c r="L8" t="n">
-        <v>67.16</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>6.71</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.04</v>
+        <v>0.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>16825</v>
+        <v>204</v>
       </c>
       <c r="R8" t="n">
-        <v>42.8</v>
+        <v>8.69</v>
       </c>
       <c r="S8" t="n">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="T8" t="n">
-        <v>145</v>
+        <v>27.97</v>
       </c>
       <c r="U8" t="n">
-        <v>264</v>
+        <v>17</v>
       </c>
       <c r="V8" t="n">
-        <v>27.38</v>
+        <v>2.73</v>
       </c>
       <c r="W8" t="n">
-        <v>25.5</v>
+        <v>13.7</v>
       </c>
       <c r="X8" t="n">
-        <v>0.64</v>
+        <v>1.86</v>
       </c>
       <c r="Y8" t="b">
         <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>5</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>5882.47</v>
+        <v>56.41</v>
       </c>
       <c r="AB8" t="n">
-        <v>4284.77</v>
+        <v>51.46</v>
       </c>
       <c r="AC8" t="n">
-        <v>44.5</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="9">
@@ -1319,13 +1319,13 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>256.53</v>
+        <v>267.6</v>
       </c>
       <c r="J9" t="n">
         <v>243.52</v>
       </c>
       <c r="K9" t="n">
-        <v>5.3</v>
+        <v>9.9</v>
       </c>
       <c r="L9" t="n">
         <v>67.65000000000001</v>
@@ -1342,13 +1342,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.165</v>
+        <v>0.157</v>
       </c>
       <c r="Q9" t="n">
-        <v>674</v>
+        <v>705</v>
       </c>
       <c r="R9" t="n">
-        <v>56.3</v>
+        <v>58.9</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1375,13 +1375,13 @@
         <v>16.21</v>
       </c>
       <c r="AA9" t="n">
-        <v>246.66</v>
+        <v>247.72</v>
       </c>
       <c r="AB9" t="n">
-        <v>178.48</v>
+        <v>179.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>73.3</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -1416,13 +1416,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>536.55</v>
+        <v>511.25</v>
       </c>
       <c r="J10" t="n">
         <v>390.61</v>
       </c>
       <c r="K10" t="n">
-        <v>37.4</v>
+        <v>30.9</v>
       </c>
       <c r="L10" t="n">
         <v>63.09</v>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.471</v>
+        <v>0.494</v>
       </c>
       <c r="Q10" t="n">
-        <v>1702</v>
+        <v>1624</v>
       </c>
       <c r="R10" t="n">
-        <v>20.2</v>
+        <v>19.2</v>
       </c>
       <c r="S10" t="n">
         <v>581</v>
@@ -1472,22 +1472,22 @@
         <v>29</v>
       </c>
       <c r="AA10" t="n">
-        <v>466.26</v>
+        <v>468.45</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>30.3</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
         <v>25</v>
@@ -1511,78 +1511,80 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>191.8</v>
+        <v>374.55</v>
       </c>
       <c r="J11" t="n">
-        <v>164.1</v>
+        <v>338.1</v>
       </c>
       <c r="K11" t="n">
-        <v>16.9</v>
+        <v>10.8</v>
       </c>
       <c r="L11" t="n">
-        <v>60.6</v>
+        <v>66.73</v>
       </c>
       <c r="M11" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.006</v>
+        <v>0.077</v>
       </c>
       <c r="Q11" t="n">
-        <v>4043</v>
-      </c>
-      <c r="R11" t="inlineStr"/>
+        <v>444</v>
+      </c>
+      <c r="R11" t="n">
+        <v>13.1</v>
+      </c>
       <c r="S11" t="n">
-        <v>39</v>
+        <v>-8</v>
       </c>
       <c r="T11" t="n">
-        <v>258</v>
+        <v>24</v>
       </c>
       <c r="U11" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.13</v>
+        <v>14.36</v>
       </c>
       <c r="W11" t="n">
-        <v>6.38</v>
+        <v>9.94</v>
       </c>
       <c r="X11" t="n">
-        <v>10.11</v>
+        <v>0.23</v>
       </c>
       <c r="Y11" t="b">
         <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>177.46</v>
+        <v>321.27</v>
       </c>
       <c r="AB11" t="n">
-        <v>178.83</v>
+        <v>260.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.2</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>SENCO GOLD LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1606,84 +1608,84 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>378.75</v>
+        <v>352.75</v>
       </c>
       <c r="J12" t="n">
-        <v>338.1</v>
+        <v>335.41</v>
       </c>
       <c r="K12" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>66.73</v>
+        <v>68.48</v>
       </c>
       <c r="M12" t="n">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.077</v>
+        <v>0.007</v>
       </c>
       <c r="Q12" t="n">
-        <v>439</v>
+        <v>5779</v>
       </c>
       <c r="R12" t="n">
-        <v>13</v>
+        <v>9.77</v>
       </c>
       <c r="S12" t="n">
-        <v>-8</v>
+        <v>43</v>
       </c>
       <c r="T12" t="n">
-        <v>24</v>
+        <v>223</v>
       </c>
       <c r="U12" t="n">
-        <v>33</v>
+        <v>175</v>
       </c>
       <c r="V12" t="n">
-        <v>14.36</v>
+        <v>6.97</v>
       </c>
       <c r="W12" t="n">
-        <v>9.94</v>
+        <v>21.4</v>
       </c>
       <c r="X12" t="n">
-        <v>0.23</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AA12" t="n">
-        <v>318.93</v>
+        <v>363.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>259.54</v>
+        <v>333.29</v>
       </c>
       <c r="AC12" t="n">
-        <v>76.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1691,96 +1693,94 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>190.05</v>
+      </c>
+      <c r="J13" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4021</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>39</v>
+      </c>
+      <c r="T13" t="n">
+        <v>258</v>
+      </c>
+      <c r="U13" t="n">
         <v>30</v>
       </c>
-      <c r="H13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I13" t="n">
-        <v>331.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>314.32</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>63.24</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="N13" t="n">
-        <v>11</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>316</v>
-      </c>
-      <c r="R13" t="n">
-        <v>146</v>
-      </c>
-      <c r="S13" t="n">
-        <v>22</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U13" t="n">
-        <v>264</v>
-      </c>
       <c r="V13" t="n">
-        <v>2.55</v>
+        <v>-1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>2.07</v>
+        <v>6.38</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01</v>
+        <v>10.11</v>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.06</v>
+        <v>61</v>
       </c>
       <c r="AA13" t="n">
-        <v>291.82</v>
+        <v>177.86</v>
       </c>
       <c r="AB13" t="n">
-        <v>276.72</v>
+        <v>178.69</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NUPUR RECYCLERS LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1788,81 +1788,81 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H14" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>122.5</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>82.93000000000001</v>
+        <v>91.62</v>
       </c>
       <c r="K14" t="n">
-        <v>47.7</v>
+        <v>7.9</v>
       </c>
       <c r="L14" t="n">
-        <v>72.53</v>
+        <v>70.88</v>
       </c>
       <c r="M14" t="n">
-        <v>0.42</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.05</v>
+        <v>0.331</v>
       </c>
       <c r="Q14" t="n">
-        <v>846</v>
+        <v>2535</v>
       </c>
       <c r="R14" t="n">
-        <v>90.40000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.43</v>
+        <v>14</v>
       </c>
       <c r="U14" t="n">
-        <v>82</v>
+        <v>-14</v>
       </c>
       <c r="V14" t="n">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
       <c r="W14" t="n">
-        <v>9.710000000000001</v>
+        <v>16.9</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.67</v>
+        <v>30</v>
       </c>
       <c r="AA14" t="n">
-        <v>106.27</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>69.42</v>
+        <v>92</v>
       </c>
       <c r="AC14" t="n">
-        <v>136.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="15">
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1894,16 +1894,16 @@
         <v>30</v>
       </c>
       <c r="H15" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="I15" t="n">
-        <v>661.2</v>
+        <v>623.1</v>
       </c>
       <c r="J15" t="n">
         <v>577.97</v>
       </c>
       <c r="K15" t="n">
-        <v>14.4</v>
+        <v>7.8</v>
       </c>
       <c r="L15" t="n">
         <v>64.68000000000001</v>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.47</v>
+        <v>0.504</v>
       </c>
       <c r="Q15" t="n">
-        <v>1235</v>
+        <v>1150</v>
       </c>
       <c r="R15" t="n">
-        <v>62.9</v>
+        <v>58.6</v>
       </c>
       <c r="S15" t="n">
         <v>21</v>
@@ -1953,28 +1953,28 @@
         <v>-110</v>
       </c>
       <c r="AA15" t="n">
-        <v>573.8099999999999</v>
+        <v>573.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>505.88</v>
+        <v>506.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>35.4</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1982,96 +1982,96 @@
         </is>
       </c>
       <c r="E16" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" t="n">
         <v>15</v>
-      </c>
-      <c r="F16" t="n">
-        <v>14</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="I16" t="n">
-        <v>501.55</v>
+        <v>339</v>
       </c>
       <c r="J16" t="n">
-        <v>476.81</v>
+        <v>314.32</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2</v>
+        <v>7.9</v>
       </c>
       <c r="L16" t="n">
-        <v>62.09</v>
+        <v>63.24</v>
       </c>
       <c r="M16" t="n">
-        <v>0.57</v>
+        <v>1.74</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.066</v>
+        <v>0.544</v>
       </c>
       <c r="Q16" t="n">
-        <v>863</v>
+        <v>320</v>
       </c>
       <c r="R16" t="n">
-        <v>8.48</v>
+        <v>148</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="T16" t="n">
-        <v>30</v>
+        <v>2.45</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="V16" t="n">
-        <v>14.66</v>
+        <v>2.55</v>
       </c>
       <c r="W16" t="n">
-        <v>14.4</v>
+        <v>2.07</v>
       </c>
       <c r="X16" t="n">
         <v>0.01</v>
       </c>
       <c r="Y16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>6.06</v>
       </c>
       <c r="AA16" t="n">
-        <v>489.19</v>
+        <v>293.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>488.9</v>
+        <v>277.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>NUPUR RECYCLERS LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2082,78 +2082,78 @@
         <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>120.05</v>
+      </c>
+      <c r="J17" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="K17" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>829</v>
+      </c>
+      <c r="R17" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U17" t="n">
+        <v>82</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W17" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>82.38</v>
-      </c>
-      <c r="J17" t="n">
-        <v>76.98</v>
-      </c>
-      <c r="K17" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" t="n">
-        <v>62.78</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>423</v>
-      </c>
-      <c r="R17" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>21</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-19</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W17" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.28</v>
       </c>
       <c r="Y17" t="b">
         <v>1</v>
       </c>
       <c r="Z17" t="n">
-        <v>41.64</v>
+        <v>3.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>75.8</v>
+        <v>107.01</v>
       </c>
       <c r="AB17" t="n">
-        <v>78.3</v>
+        <v>69.69</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.3</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="18">
@@ -2188,13 +2188,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>19.52</v>
+        <v>19.84</v>
       </c>
       <c r="J18" t="n">
         <v>21.01</v>
       </c>
       <c r="K18" t="n">
-        <v>-7.1</v>
+        <v>-5.6</v>
       </c>
       <c r="L18" t="n">
         <v>70.87</v>
@@ -2211,13 +2211,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="Q18" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="R18" t="n">
-        <v>6.03</v>
+        <v>6.09</v>
       </c>
       <c r="S18" t="n">
         <v>118</v>
@@ -2240,28 +2240,28 @@
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
-        <v>17.99</v>
+        <v>18.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>15.1</v>
+        <v>15.11</v>
       </c>
       <c r="AC18" t="n">
-        <v>36.1</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RGL</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Renaissance Global Limited</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2269,92 +2269,92 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>135.22</v>
+        <v>82.91</v>
       </c>
       <c r="J19" t="n">
-        <v>100.9</v>
+        <v>76.98</v>
       </c>
       <c r="K19" t="n">
-        <v>34</v>
+        <v>7.7</v>
       </c>
       <c r="L19" t="n">
-        <v>69.56</v>
+        <v>62.78</v>
       </c>
       <c r="M19" t="n">
-        <v>3.01</v>
+        <v>2.64</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.207</v>
+        <v>0.617</v>
       </c>
       <c r="Q19" t="n">
-        <v>1455</v>
+        <v>428</v>
       </c>
       <c r="R19" t="n">
-        <v>50.8</v>
+        <v>39.7</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="T19" t="n">
-        <v>22</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="V19" t="n">
-        <v>0.95</v>
+        <v>1.54</v>
       </c>
       <c r="W19" t="n">
-        <v>5.28</v>
+        <v>8.73</v>
       </c>
       <c r="X19" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="Y19" t="b">
         <v>1</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>41.64</v>
       </c>
       <c r="AA19" t="n">
-        <v>121.5</v>
+        <v>75.88</v>
       </c>
       <c r="AB19" t="n">
-        <v>115.45</v>
+        <v>78.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.7</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>RGL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>Renaissance Global Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2366,78 +2366,78 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>98.73999999999999</v>
+        <v>136.96</v>
       </c>
       <c r="J20" t="n">
-        <v>89.34</v>
+        <v>100.9</v>
       </c>
       <c r="K20" t="n">
-        <v>10.5</v>
+        <v>35.7</v>
       </c>
       <c r="L20" t="n">
-        <v>70.88</v>
+        <v>69.56</v>
       </c>
       <c r="M20" t="n">
-        <v>6.25</v>
+        <v>3.01</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="Q20" t="n">
-        <v>2533</v>
+        <v>1470</v>
       </c>
       <c r="R20" t="n">
-        <v>20.7</v>
+        <v>51.3</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="U20" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.57</v>
+        <v>0.95</v>
       </c>
       <c r="W20" t="n">
-        <v>16.9</v>
+        <v>5.28</v>
       </c>
       <c r="X20" t="n">
-        <v>0.01</v>
+        <v>0.52</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>90.45</v>
+        <v>121.96</v>
       </c>
       <c r="AB20" t="n">
-        <v>91.98999999999999</v>
+        <v>115.45</v>
       </c>
       <c r="AC20" t="n">
         <v>6.8</v>
@@ -2446,16 +2446,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>DIAMONDYD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SENCO GOLD LIMITED</t>
+          <t>Prataap Snacks Limited</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,96 +2463,96 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F21" t="n">
         <v>21</v>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="I21" t="n">
-        <v>348.6</v>
+        <v>1144.8</v>
       </c>
       <c r="J21" t="n">
-        <v>335.41</v>
+        <v>1174.34</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>-2.5</v>
       </c>
       <c r="L21" t="n">
-        <v>68.48</v>
+        <v>69.75</v>
       </c>
       <c r="M21" t="n">
-        <v>0.41</v>
+        <v>65.58</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.007</v>
+        <v>2.393</v>
       </c>
       <c r="Q21" t="n">
-        <v>5718</v>
+        <v>2741</v>
       </c>
       <c r="R21" t="n">
-        <v>9.66</v>
+        <v>215</v>
       </c>
       <c r="S21" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>223</v>
+        <v>19.05</v>
       </c>
       <c r="U21" t="n">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="V21" t="n">
-        <v>6.97</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>21.4</v>
+        <v>3.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>0.06</v>
       </c>
       <c r="Y21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>7</v>
+        <v>3.87</v>
       </c>
       <c r="AA21" t="n">
-        <v>362.97</v>
+        <v>1165.18</v>
       </c>
       <c r="AB21" t="n">
-        <v>333.21</v>
+        <v>1085.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DIAMONDYD</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Prataap Snacks Limited</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2560,81 +2560,81 @@
         </is>
       </c>
       <c r="E22" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" t="n">
+        <v>14</v>
+      </c>
+      <c r="G22" t="n">
         <v>25</v>
       </c>
-      <c r="F22" t="n">
-        <v>21</v>
-      </c>
-      <c r="G22" t="n">
-        <v>15</v>
-      </c>
       <c r="H22" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1147.1</v>
+        <v>494.45</v>
       </c>
       <c r="J22" t="n">
-        <v>1174.34</v>
+        <v>479.69</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.3</v>
+        <v>3.1</v>
       </c>
       <c r="L22" t="n">
-        <v>69.75</v>
+        <v>62.09</v>
       </c>
       <c r="M22" t="n">
-        <v>65.58</v>
+        <v>0.66</v>
       </c>
       <c r="N22" t="n">
         <v>5</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.393</v>
+        <v>0.078</v>
       </c>
       <c r="Q22" t="n">
-        <v>2741</v>
+        <v>849</v>
       </c>
       <c r="R22" t="n">
-        <v>215</v>
+        <v>8.35</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>19.05</v>
+        <v>30</v>
       </c>
       <c r="U22" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>14.66</v>
       </c>
       <c r="W22" t="n">
-        <v>3.08</v>
+        <v>14.4</v>
       </c>
       <c r="X22" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="Y22" t="b">
         <v>1</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.87</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="n">
-        <v>1164.41</v>
+        <v>489.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1084.8</v>
+        <v>488.67</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -2669,7 +2669,7 @@
         <v>-3</v>
       </c>
       <c r="I23" t="n">
-        <v>28.04</v>
+        <v>28.03</v>
       </c>
       <c r="J23" t="n">
         <v>29.14</v>
@@ -2692,13 +2692,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.229</v>
+        <v>1.207</v>
       </c>
       <c r="Q23" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="R23" t="n">
-        <v>78.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="S23" t="n">
         <v>-1</v>
@@ -2725,13 +2725,13 @@
         <v>21.51</v>
       </c>
       <c r="AA23" t="n">
-        <v>27.37</v>
+        <v>27.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>24.61</v>
+        <v>24.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>34.2</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="24">
@@ -2766,13 +2766,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1312.2</v>
+        <v>1351.4</v>
       </c>
       <c r="J24" t="n">
         <v>1104.34</v>
       </c>
       <c r="K24" t="n">
-        <v>18.8</v>
+        <v>22.4</v>
       </c>
       <c r="L24" t="n">
         <v>60.82</v>
@@ -2792,10 +2792,10 @@
         <v>0.001</v>
       </c>
       <c r="Q24" t="n">
-        <v>355979</v>
+        <v>367621</v>
       </c>
       <c r="R24" t="n">
-        <v>19.6</v>
+        <v>20.2</v>
       </c>
       <c r="S24" t="n">
         <v>7</v>
@@ -2822,24 +2822,24 @@
         <v>29</v>
       </c>
       <c r="AA24" t="n">
-        <v>1249.68</v>
+        <v>1254.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>1395.25</v>
+        <v>1394.31</v>
       </c>
       <c r="AC24" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2851,92 +2851,96 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G25" t="n">
         <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>13.79</v>
+        <v>124.56</v>
       </c>
       <c r="J25" t="n">
-        <v>12.34</v>
+        <v>105.19</v>
       </c>
       <c r="K25" t="n">
-        <v>11.8</v>
+        <v>18.4</v>
       </c>
       <c r="L25" t="n">
-        <v>69.12</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>1.38</v>
+        <v>2.63</v>
       </c>
       <c r="N25" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.354</v>
+        <v>0.052</v>
       </c>
       <c r="Q25" t="n">
-        <v>390</v>
+        <v>5034</v>
       </c>
       <c r="R25" t="n">
-        <v>1259</v>
+        <v>32.8</v>
       </c>
       <c r="S25" t="n">
-        <v>-61</v>
-      </c>
-      <c r="T25" t="inlineStr"/>
+        <v>-25</v>
+      </c>
+      <c r="T25" t="n">
+        <v>71</v>
+      </c>
       <c r="U25" t="n">
-        <v>-98</v>
+        <v>-11</v>
       </c>
       <c r="V25" t="n">
-        <v>0.01</v>
+        <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>2.46</v>
+        <v>10.7</v>
       </c>
       <c r="X25" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
       </c>
-      <c r="Z25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>69</v>
+      </c>
       <c r="AA25" t="n">
-        <v>11.11</v>
+        <v>106.06</v>
       </c>
       <c r="AB25" t="n">
-        <v>13.53</v>
+        <v>112.27</v>
       </c>
       <c r="AC25" t="n">
-        <v>-8.9</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2944,189 +2948,189 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>122.62</v>
+        <v>168.2</v>
       </c>
       <c r="J26" t="n">
-        <v>105.19</v>
+        <v>201.21</v>
       </c>
       <c r="K26" t="n">
-        <v>16.6</v>
+        <v>-16.4</v>
       </c>
       <c r="L26" t="n">
-        <v>67.15000000000001</v>
+        <v>64.08</v>
       </c>
       <c r="M26" t="n">
-        <v>2.63</v>
+        <v>8.07</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.053</v>
+        <v>1.189</v>
       </c>
       <c r="Q26" t="n">
-        <v>4950</v>
+        <v>679</v>
       </c>
       <c r="R26" t="n">
-        <v>32.3</v>
+        <v>15</v>
       </c>
       <c r="S26" t="n">
-        <v>-25</v>
+        <v>-1</v>
       </c>
       <c r="T26" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="U26" t="n">
-        <v>-11</v>
+        <v>45</v>
       </c>
       <c r="V26" t="n">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="W26" t="n">
-        <v>10.7</v>
+        <v>19.4</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Y26" t="b">
         <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="AA26" t="n">
-        <v>105.7</v>
+        <v>176.27</v>
       </c>
       <c r="AB26" t="n">
-        <v>112.32</v>
+        <v>199.59</v>
       </c>
       <c r="AC26" t="n">
-        <v>13.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>THOMAS COOK (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Buy on Breakout</t>
+          <t>Watchlist</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>171.15</v>
+        <v>105.71</v>
       </c>
       <c r="J27" t="n">
-        <v>201.21</v>
+        <v>109.31</v>
       </c>
       <c r="K27" t="n">
-        <v>-14.9</v>
+        <v>-3.3</v>
       </c>
       <c r="L27" t="n">
-        <v>64.08</v>
+        <v>72.34</v>
       </c>
       <c r="M27" t="n">
-        <v>8.07</v>
+        <v>48.4</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.168</v>
+        <v>0.971</v>
       </c>
       <c r="Q27" t="n">
-        <v>691</v>
+        <v>4985</v>
       </c>
       <c r="R27" t="n">
-        <v>15.2</v>
+        <v>40</v>
       </c>
       <c r="S27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="U27" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="V27" t="n">
-        <v>3.1</v>
+        <v>1.25</v>
       </c>
       <c r="W27" t="n">
-        <v>19.4</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="Y27" t="b">
         <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>176.93</v>
+        <v>105.29</v>
       </c>
       <c r="AB27" t="n">
-        <v>200.19</v>
+        <v>113.77</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>THOMAS COOK (INDIA) LIMITED</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3138,78 +3142,78 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>107.92</v>
+        <v>508.8</v>
       </c>
       <c r="J28" t="n">
-        <v>109.31</v>
+        <v>545.03</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.3</v>
+        <v>-6.6</v>
       </c>
       <c r="L28" t="n">
-        <v>72.34</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>48.4</v>
+        <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.954</v>
+        <v>0.034</v>
       </c>
       <c r="Q28" t="n">
-        <v>5075</v>
+        <v>3207</v>
       </c>
       <c r="R28" t="n">
-        <v>40.7</v>
+        <v>21.7</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T28" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="U28" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="V28" t="n">
-        <v>1.25</v>
+        <v>3.73</v>
       </c>
       <c r="W28" t="n">
-        <v>9.710000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="X28" t="n">
-        <v>0.06</v>
+        <v>0.62</v>
       </c>
       <c r="Y28" t="b">
         <v>1</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AA28" t="n">
-        <v>105.47</v>
+        <v>528.83</v>
       </c>
       <c r="AB28" t="n">
-        <v>114.01</v>
+        <v>562.2</v>
       </c>
       <c r="AC28" t="n">
         <v>0.7</v>
@@ -3218,16 +3222,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>BAJAJHCARE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>BAJAJ HEALTHCARE LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3235,10 +3239,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F29" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G29" t="n">
         <v>5</v>
@@ -3247,69 +3251,69 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>508.75</v>
+        <v>329</v>
       </c>
       <c r="J29" t="n">
-        <v>545.03</v>
+        <v>297.3</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.7</v>
+        <v>10.7</v>
       </c>
       <c r="L29" t="n">
-        <v>69.90000000000001</v>
+        <v>67.69</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>2.97</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.034</v>
+        <v>0.268</v>
       </c>
       <c r="Q29" t="n">
-        <v>3213</v>
+        <v>1108</v>
       </c>
       <c r="R29" t="n">
-        <v>21.8</v>
+        <v>19.7</v>
       </c>
       <c r="S29" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T29" t="n">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="U29" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="V29" t="n">
-        <v>3.73</v>
+        <v>4.07</v>
       </c>
       <c r="W29" t="n">
-        <v>19.8</v>
+        <v>11.5</v>
       </c>
       <c r="X29" t="n">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="Y29" t="b">
         <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="AA29" t="n">
-        <v>529.98</v>
+        <v>334.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>562.66</v>
+        <v>348.71</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.9</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="30">
@@ -3344,36 +3348,36 @@
         <v>-2</v>
       </c>
       <c r="I30" t="n">
-        <v>209.94</v>
+        <v>207.76</v>
       </c>
       <c r="J30" t="n">
-        <v>209.98</v>
+        <v>210.35</v>
       </c>
       <c r="K30" t="n">
-        <v>-0</v>
+        <v>-1.2</v>
       </c>
       <c r="L30" t="n">
         <v>67.04000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.129</v>
+        <v>0.147</v>
       </c>
       <c r="Q30" t="n">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="R30" t="n">
-        <v>25.1</v>
+        <v>24.5</v>
       </c>
       <c r="S30" t="n">
         <v>12</v>
@@ -3400,28 +3404,28 @@
         <v>3.16</v>
       </c>
       <c r="AA30" t="n">
-        <v>206.87</v>
+        <v>207.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>194.94</v>
+        <v>194.97</v>
       </c>
       <c r="AC30" t="n">
-        <v>10.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BAJAJ HEALTHCARE LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3429,96 +3433,96 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>333.7</v>
+        <v>171.12</v>
       </c>
       <c r="J31" t="n">
-        <v>297.3</v>
+        <v>175.74</v>
       </c>
       <c r="K31" t="n">
-        <v>12.2</v>
+        <v>-2.6</v>
       </c>
       <c r="L31" t="n">
-        <v>67.69</v>
+        <v>74.59</v>
       </c>
       <c r="M31" t="n">
-        <v>2.97</v>
+        <v>0.49</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.264</v>
+        <v>0.023</v>
       </c>
       <c r="Q31" t="n">
-        <v>1123</v>
+        <v>2168</v>
       </c>
       <c r="R31" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="S31" t="n">
         <v>20</v>
       </c>
-      <c r="S31" t="n">
-        <v>12</v>
-      </c>
       <c r="T31" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="U31" t="n">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="V31" t="n">
-        <v>4.07</v>
+        <v>0.8</v>
       </c>
       <c r="W31" t="n">
-        <v>11.5</v>
+        <v>30.3</v>
       </c>
       <c r="X31" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="Y31" t="b">
         <v>1</v>
       </c>
       <c r="Z31" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA31" t="n">
-        <v>334.18</v>
+        <v>191.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>349.24</v>
+        <v>550.58</v>
       </c>
       <c r="AC31" t="n">
-        <v>-2.4</v>
+        <v>-88.09999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3526,81 +3530,77 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F32" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="I32" t="n">
-        <v>172.27</v>
+        <v>13.34</v>
       </c>
       <c r="J32" t="n">
-        <v>180.98</v>
+        <v>12.4</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.8</v>
+        <v>7.6</v>
       </c>
       <c r="L32" t="n">
-        <v>74.59</v>
+        <v>69.12</v>
       </c>
       <c r="M32" t="n">
-        <v>0.25</v>
+        <v>1.46</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.011</v>
+        <v>0.385</v>
       </c>
       <c r="Q32" t="n">
-        <v>2186</v>
+        <v>379</v>
       </c>
       <c r="R32" t="n">
-        <v>50.2</v>
+        <v>1221</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
-      </c>
-      <c r="T32" t="n">
-        <v>17</v>
-      </c>
+        <v>-61</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="n">
-        <v>83</v>
+        <v>-98</v>
       </c>
       <c r="V32" t="n">
-        <v>0.8</v>
+        <v>0.01</v>
       </c>
       <c r="W32" t="n">
-        <v>30.3</v>
+        <v>2.46</v>
       </c>
       <c r="X32" t="n">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="Y32" t="b">
         <v>1</v>
       </c>
-      <c r="Z32" t="n">
-        <v>23</v>
-      </c>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="n">
-        <v>192.11</v>
+        <v>11.16</v>
       </c>
       <c r="AB32" t="n">
-        <v>553.8</v>
+        <v>13.51</v>
       </c>
       <c r="AC32" t="n">
-        <v>-88</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="33">
@@ -3635,13 +3635,13 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>263.7</v>
+        <v>259.35</v>
       </c>
       <c r="J33" t="n">
         <v>257.65</v>
       </c>
       <c r="K33" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="L33" t="n">
         <v>70.09</v>
@@ -3658,13 +3658,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="Q33" t="n">
-        <v>2692</v>
+        <v>2649</v>
       </c>
       <c r="R33" t="n">
-        <v>46.9</v>
+        <v>46.1</v>
       </c>
       <c r="S33" t="n">
         <v>-3</v>
@@ -3691,24 +3691,24 @@
         <v>24</v>
       </c>
       <c r="AA33" t="n">
-        <v>294.06</v>
+        <v>293.68</v>
       </c>
       <c r="AB33" t="n">
-        <v>277.53</v>
+        <v>277.19</v>
       </c>
       <c r="AC33" t="n">
-        <v>5.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3720,90 +3720,90 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F34" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I34" t="n">
-        <v>746</v>
+        <v>55.04</v>
       </c>
       <c r="J34" t="n">
-        <v>717.77</v>
+        <v>53.49</v>
       </c>
       <c r="K34" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="L34" t="n">
-        <v>61.71</v>
+        <v>67.23</v>
       </c>
       <c r="M34" t="n">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.697</v>
+        <v>1.716</v>
       </c>
       <c r="Q34" t="n">
-        <v>231</v>
+        <v>116</v>
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T34" t="n">
-        <v>11.91</v>
+        <v>2.47</v>
       </c>
       <c r="U34" t="n">
-        <v>-184</v>
+        <v>-3779</v>
       </c>
       <c r="V34" t="n">
-        <v>31.98</v>
+        <v>-0.05</v>
       </c>
       <c r="W34" t="n">
-        <v>0.27</v>
+        <v>-1.26</v>
       </c>
       <c r="X34" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Y34" t="b">
         <v>1</v>
       </c>
       <c r="Z34" t="n">
-        <v>57.93</v>
+        <v>3</v>
       </c>
       <c r="AA34" t="n">
-        <v>730.96</v>
+        <v>54.18</v>
       </c>
       <c r="AB34" t="n">
-        <v>760.88</v>
+        <v>55.11</v>
       </c>
       <c r="AC34" t="n">
-        <v>-3.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3818,76 +3818,76 @@
         <v>20</v>
       </c>
       <c r="F35" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>174.16</v>
+        <v>739.5</v>
       </c>
       <c r="J35" t="n">
-        <v>182.69</v>
+        <v>717.77</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.7</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>69.05</v>
+        <v>61.71</v>
       </c>
       <c r="M35" t="n">
-        <v>0.74</v>
+        <v>1.61</v>
       </c>
       <c r="N35" t="n">
         <v>3</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.124</v>
+        <v>0.703</v>
       </c>
       <c r="Q35" t="n">
-        <v>597</v>
-      </c>
-      <c r="R35" t="n">
-        <v>14.2</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>15</v>
+        <v>11.91</v>
       </c>
       <c r="U35" t="n">
-        <v>82</v>
+        <v>-184</v>
       </c>
       <c r="V35" t="n">
-        <v>3.07</v>
+        <v>31.98</v>
       </c>
       <c r="W35" t="n">
-        <v>42.7</v>
+        <v>0.27</v>
       </c>
       <c r="X35" t="n">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="Y35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="n">
-        <v>12</v>
+        <v>57.93</v>
       </c>
       <c r="AA35" t="n">
-        <v>171.66</v>
-      </c>
-      <c r="AB35" t="inlineStr"/>
+        <v>730.45</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>761.02</v>
+      </c>
       <c r="AC35" t="n">
-        <v>-9.9</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="36">
@@ -3922,13 +3922,13 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>116.9</v>
+        <v>115.67</v>
       </c>
       <c r="J36" t="n">
         <v>114.86</v>
       </c>
       <c r="K36" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="L36" t="n">
         <v>69.73999999999999</v>
@@ -3945,13 +3945,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.32</v>
+        <v>0.323</v>
       </c>
       <c r="Q36" t="n">
-        <v>2302</v>
+        <v>2279</v>
       </c>
       <c r="R36" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="S36" t="n">
         <v>18</v>
@@ -3978,28 +3978,28 @@
         <v>38</v>
       </c>
       <c r="AA36" t="n">
-        <v>125.82</v>
+        <v>125.35</v>
       </c>
       <c r="AB36" t="n">
-        <v>323.31</v>
+        <v>318.92</v>
       </c>
       <c r="AC36" t="n">
-        <v>-12.5</v>
+        <v>-12.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4007,96 +4007,94 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>268.95</v>
+        <v>740.55</v>
       </c>
       <c r="J37" t="n">
-        <v>269.7</v>
+        <v>815.16</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.3</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>73.09</v>
+        <v>73.2</v>
       </c>
       <c r="M37" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.097</v>
+        <v>0.165</v>
       </c>
       <c r="Q37" t="n">
-        <v>1531</v>
+        <v>750</v>
       </c>
       <c r="R37" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>185</v>
       </c>
       <c r="T37" t="n">
-        <v>46</v>
+        <v>11.55</v>
       </c>
       <c r="U37" t="n">
-        <v>18</v>
+        <v>204</v>
       </c>
       <c r="V37" t="n">
-        <v>4.31</v>
+        <v>6.84</v>
       </c>
       <c r="W37" t="n">
-        <v>13.6</v>
+        <v>50.7</v>
       </c>
       <c r="X37" t="n">
-        <v>0.28</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y37" t="b">
         <v>1</v>
       </c>
       <c r="Z37" t="n">
-        <v>12</v>
+        <v>16.07</v>
       </c>
       <c r="AA37" t="n">
-        <v>268.06</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>294</v>
-      </c>
+        <v>746.15</v>
+      </c>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-8.800000000000001</v>
+        <v>-18.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4104,107 +4102,107 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H38" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>41.65</v>
+        <v>428.15</v>
       </c>
       <c r="J38" t="n">
-        <v>43.04</v>
+        <v>474.82</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.2</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>71.79000000000001</v>
+        <v>70.55</v>
       </c>
       <c r="M38" t="n">
-        <v>1.02</v>
+        <v>10.22</v>
       </c>
       <c r="N38" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.247</v>
+        <v>0.277</v>
       </c>
       <c r="Q38" t="n">
-        <v>413</v>
+        <v>3684</v>
       </c>
       <c r="R38" t="n">
-        <v>102</v>
+        <v>25.8</v>
       </c>
       <c r="S38" t="n">
-        <v>246</v>
+        <v>2</v>
       </c>
       <c r="T38" t="n">
-        <v>0.91</v>
+        <v>127</v>
       </c>
       <c r="U38" t="n">
-        <v>10</v>
+        <v>-14</v>
       </c>
       <c r="V38" t="n">
-        <v>0.14</v>
+        <v>6.41</v>
       </c>
       <c r="W38" t="n">
-        <v>2.16</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y38" t="b">
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.21</v>
+        <v>21</v>
       </c>
       <c r="AA38" t="n">
-        <v>40.75</v>
+        <v>448.37</v>
       </c>
       <c r="AB38" t="n">
-        <v>39.66</v>
+        <v>434.13</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>20</v>
       </c>
       <c r="F39" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -4213,179 +4211,179 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>727.55</v>
+        <v>169.08</v>
       </c>
       <c r="J39" t="n">
-        <v>815.16</v>
+        <v>182.69</v>
       </c>
       <c r="K39" t="n">
-        <v>-10.7</v>
+        <v>-7.4</v>
       </c>
       <c r="L39" t="n">
-        <v>73.2</v>
+        <v>69.05</v>
       </c>
       <c r="M39" t="n">
-        <v>1.24</v>
+        <v>0.74</v>
       </c>
       <c r="N39" t="n">
         <v>3</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.168</v>
+        <v>0.128</v>
       </c>
       <c r="Q39" t="n">
-        <v>737</v>
+        <v>580</v>
       </c>
       <c r="R39" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="S39" t="n">
-        <v>185</v>
+        <v>61</v>
       </c>
       <c r="T39" t="n">
-        <v>11.55</v>
+        <v>15</v>
       </c>
       <c r="U39" t="n">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="V39" t="n">
-        <v>6.84</v>
+        <v>3.07</v>
       </c>
       <c r="W39" t="n">
-        <v>50.7</v>
+        <v>42.7</v>
       </c>
       <c r="X39" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="Y39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>16.07</v>
+        <v>12</v>
       </c>
       <c r="AA39" t="n">
-        <v>748.38</v>
+        <v>171.39</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>-20</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>25</v>
       </c>
       <c r="F40" t="n">
+        <v>11</v>
+      </c>
+      <c r="G40" t="n">
         <v>5</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>111.83</v>
+      </c>
+      <c r="J40" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N40" t="n">
         <v>10</v>
       </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>429.6</v>
-      </c>
-      <c r="J40" t="n">
-        <v>474.82</v>
-      </c>
-      <c r="K40" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="L40" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="M40" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5</v>
-      </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.277</v>
+        <v>0.282</v>
       </c>
       <c r="Q40" t="n">
-        <v>3689</v>
+        <v>213</v>
       </c>
       <c r="R40" t="n">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="T40" t="n">
-        <v>127</v>
+        <v>12.07</v>
       </c>
       <c r="U40" t="n">
-        <v>-14</v>
+        <v>-29</v>
       </c>
       <c r="V40" t="n">
-        <v>6.41</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
-        <v>9.890000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="X40" t="n">
-        <v>1.05</v>
+        <v>0.98</v>
       </c>
       <c r="Y40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="n">
-        <v>21</v>
+        <v>4.11</v>
       </c>
       <c r="AA40" t="n">
-        <v>449.41</v>
+        <v>111.31</v>
       </c>
       <c r="AB40" t="n">
-        <v>434.38</v>
+        <v>119.92</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.5</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4393,94 +4391,96 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="G41" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>-2</v>
       </c>
       <c r="I41" t="n">
-        <v>54.82</v>
+        <v>55.28</v>
       </c>
       <c r="J41" t="n">
-        <v>53.49</v>
+        <v>60.15</v>
       </c>
       <c r="K41" t="n">
-        <v>2.5</v>
+        <v>-8.1</v>
       </c>
       <c r="L41" t="n">
-        <v>67.23</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>1.99</v>
+        <v>0.9</v>
       </c>
       <c r="N41" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.716</v>
+        <v>0.188</v>
       </c>
       <c r="Q41" t="n">
-        <v>116</v>
-      </c>
-      <c r="R41" t="inlineStr"/>
+        <v>480</v>
+      </c>
+      <c r="R41" t="n">
+        <v>12</v>
+      </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="T41" t="n">
-        <v>2.47</v>
+        <v>21</v>
       </c>
       <c r="U41" t="n">
-        <v>-3779</v>
+        <v>20</v>
       </c>
       <c r="V41" t="n">
-        <v>-0.05</v>
+        <v>1.22</v>
       </c>
       <c r="W41" t="n">
-        <v>-1.26</v>
+        <v>12</v>
       </c>
       <c r="X41" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Y41" t="b">
         <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>54.21</v>
+        <v>57.78</v>
       </c>
       <c r="AB41" t="n">
-        <v>55.12</v>
+        <v>59.21</v>
       </c>
       <c r="AC41" t="n">
-        <v>-1.7</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4488,82 +4488,92 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F42" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>67.40000000000001</v>
+        <v>266.6</v>
       </c>
       <c r="J42" t="n">
-        <v>64.04000000000001</v>
+        <v>269.7</v>
       </c>
       <c r="K42" t="n">
-        <v>5.2</v>
+        <v>-1.1</v>
       </c>
       <c r="L42" t="n">
-        <v>64.29000000000001</v>
+        <v>73.09</v>
       </c>
       <c r="M42" t="n">
-        <v>0.31</v>
+        <v>1.48</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.037</v>
+        <v>0.098</v>
       </c>
       <c r="Q42" t="n">
-        <v>828</v>
+        <v>1510</v>
       </c>
       <c r="R42" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S42" t="inlineStr"/>
+        <v>13.6</v>
+      </c>
+      <c r="S42" t="n">
+        <v>6</v>
+      </c>
       <c r="T42" t="n">
-        <v>12.31</v>
-      </c>
-      <c r="U42" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="U42" t="n">
+        <v>18</v>
+      </c>
       <c r="V42" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W42" t="inlineStr"/>
+        <v>4.31</v>
+      </c>
+      <c r="W42" t="n">
+        <v>13.6</v>
+      </c>
       <c r="X42" t="n">
-        <v>0.11</v>
+        <v>0.28</v>
       </c>
       <c r="Y42" t="b">
         <v>1</v>
       </c>
       <c r="Z42" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="AA42" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
+        <v>268.2</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>293.62</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>-7.5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4575,81 +4585,81 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F43" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G43" t="n">
+        <v>15</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I43" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="J43" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N43" t="n">
+        <v>22</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>26-08-2026</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>412</v>
+      </c>
+      <c r="R43" t="n">
+        <v>102</v>
+      </c>
+      <c r="S43" t="n">
+        <v>246</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="U43" t="n">
+        <v>10</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W43" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I43" t="n">
-        <v>56.57</v>
-      </c>
-      <c r="J43" t="n">
-        <v>60.15</v>
-      </c>
-      <c r="K43" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L43" t="n">
-        <v>73.01000000000001</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
-      <c r="P43" t="n">
-        <v>0.183</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>491</v>
-      </c>
-      <c r="R43" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="S43" t="n">
-        <v>19</v>
-      </c>
-      <c r="T43" t="n">
-        <v>21</v>
-      </c>
-      <c r="U43" t="n">
-        <v>20</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W43" t="n">
-        <v>12</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0.58</v>
-      </c>
       <c r="Y43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.4</v>
+        <v>4.21</v>
       </c>
       <c r="AA43" t="n">
-        <v>57.85</v>
+        <v>40.71</v>
       </c>
       <c r="AB43" t="n">
-        <v>59.27</v>
+        <v>39.67</v>
       </c>
       <c r="AC43" t="n">
-        <v>-6.3</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="44">
@@ -4684,13 +4694,13 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>86.47</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="J44" t="n">
         <v>95.54000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-9.5</v>
+        <v>-10.7</v>
       </c>
       <c r="L44" t="n">
         <v>71.72</v>
@@ -4707,13 +4717,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.607</v>
+        <v>0.615</v>
       </c>
       <c r="Q44" t="n">
-        <v>1790</v>
+        <v>1768</v>
       </c>
       <c r="R44" t="n">
-        <v>32.3</v>
+        <v>31.9</v>
       </c>
       <c r="S44" t="n">
         <v>39</v>
@@ -4740,13 +4750,13 @@
         <v>9</v>
       </c>
       <c r="AA44" t="n">
-        <v>91.40000000000001</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="AB44" t="n">
-        <v>189.83</v>
+        <v>188.11</v>
       </c>
       <c r="AC44" t="n">
-        <v>-45.8</v>
+        <v>-48.1</v>
       </c>
     </row>
     <row r="45">
@@ -4781,13 +4791,13 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>173.61</v>
+        <v>173.3</v>
       </c>
       <c r="J45" t="n">
         <v>173.91</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="L45" t="n">
         <v>65.64</v>
@@ -4804,10 +4814,10 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.135</v>
+        <v>0.136</v>
       </c>
       <c r="Q45" t="n">
-        <v>1928</v>
+        <v>1924</v>
       </c>
       <c r="R45" t="n">
         <v>20.4</v>
@@ -4837,28 +4847,28 @@
         <v>36</v>
       </c>
       <c r="AA45" t="n">
-        <v>183.78</v>
+        <v>183.62</v>
       </c>
       <c r="AB45" t="n">
-        <v>190.63</v>
+        <v>190.35</v>
       </c>
       <c r="AC45" t="n">
-        <v>-16.7</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>MBEL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>M &amp; B Engineering Limited</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4869,93 +4879,93 @@
         <v>20</v>
       </c>
       <c r="F46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>111.85</v>
+        <v>265.6</v>
       </c>
       <c r="J46" t="n">
-        <v>114.25</v>
+        <v>292.28</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.1</v>
+        <v>-9.1</v>
       </c>
       <c r="L46" t="n">
-        <v>73.48</v>
+        <v>70.45</v>
       </c>
       <c r="M46" t="n">
-        <v>0.43</v>
+        <v>1.29</v>
       </c>
       <c r="N46" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.201</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="Q46" t="n">
-        <v>214</v>
+        <v>1512</v>
       </c>
       <c r="R46" t="n">
-        <v>25.5</v>
+        <v>19.2</v>
       </c>
       <c r="S46" t="n">
+        <v>13</v>
+      </c>
+      <c r="T46" t="n">
         <v>21</v>
       </c>
-      <c r="T46" t="n">
-        <v>12.07</v>
-      </c>
       <c r="U46" t="n">
-        <v>-29</v>
+        <v>-4</v>
       </c>
       <c r="V46" t="n">
-        <v>1.02</v>
+        <v>2.56</v>
       </c>
       <c r="W46" t="n">
-        <v>7.92</v>
+        <v>19.9</v>
       </c>
       <c r="X46" t="n">
-        <v>0.98</v>
+        <v>0.13</v>
       </c>
       <c r="Y46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.11</v>
+        <v>8</v>
       </c>
       <c r="AA46" t="n">
-        <v>111.43</v>
+        <v>297.01</v>
       </c>
       <c r="AB46" t="n">
-        <v>120.06</v>
+        <v>322.67</v>
       </c>
       <c r="AC46" t="n">
-        <v>-2.9</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MBEL</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>M &amp; B Engineering Limited</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4972,170 +4982,160 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I47" t="n">
-        <v>267.25</v>
+        <v>28.15</v>
       </c>
       <c r="J47" t="n">
-        <v>292.28</v>
+        <v>34.54</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.6</v>
+        <v>-18.5</v>
       </c>
       <c r="L47" t="n">
-        <v>70.45</v>
+        <v>61.81</v>
       </c>
       <c r="M47" t="n">
-        <v>1.29</v>
+        <v>0.88</v>
       </c>
       <c r="N47" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.294</v>
       </c>
       <c r="Q47" t="n">
-        <v>1521</v>
+        <v>299</v>
       </c>
       <c r="R47" t="n">
-        <v>19.3</v>
+        <v>15.8</v>
       </c>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T47" t="n">
-        <v>21</v>
+        <v>2.79</v>
       </c>
       <c r="U47" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
       <c r="V47" t="n">
-        <v>2.56</v>
+        <v>0.21</v>
       </c>
       <c r="W47" t="n">
-        <v>19.9</v>
+        <v>17.6</v>
       </c>
       <c r="X47" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="Y47" t="b">
         <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>8</v>
+        <v>1.83</v>
       </c>
       <c r="AA47" t="n">
-        <v>297.93</v>
+        <v>30.89</v>
       </c>
       <c r="AB47" t="n">
-        <v>323.91</v>
+        <v>33.18</v>
       </c>
       <c r="AC47" t="n">
-        <v>-15.2</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H48" t="n">
         <v>0</v>
       </c>
-      <c r="H48" t="n">
-        <v>-2</v>
-      </c>
       <c r="I48" t="n">
-        <v>28.26</v>
+        <v>66.19</v>
       </c>
       <c r="J48" t="n">
-        <v>34.54</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-18.2</v>
+        <v>3.4</v>
       </c>
       <c r="L48" t="n">
-        <v>61.81</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>0.88</v>
+        <v>0.31</v>
       </c>
       <c r="N48" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.297</v>
+        <v>0.038</v>
       </c>
       <c r="Q48" t="n">
-        <v>296</v>
+        <v>807</v>
       </c>
       <c r="R48" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="S48" t="n">
-        <v>16</v>
-      </c>
+        <v>19.3</v>
+      </c>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U48" t="n">
-        <v>-30</v>
-      </c>
+        <v>12.31</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="W48" t="n">
-        <v>17.6</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="W48" t="inlineStr"/>
       <c r="X48" t="n">
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
       <c r="Y48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.83</v>
+        <v>12.14</v>
       </c>
       <c r="AA48" t="n">
-        <v>31.07</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>33.25</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>-11.4</v>
-      </c>
+        <v>66.77</v>
+      </c>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5169,13 +5169,13 @@
         <v>-2</v>
       </c>
       <c r="I49" t="n">
-        <v>84.01000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="J49" t="n">
         <v>100.33</v>
       </c>
       <c r="K49" t="n">
-        <v>-16.3</v>
+        <v>-15.4</v>
       </c>
       <c r="L49" t="n">
         <v>71.89</v>
@@ -5195,10 +5195,10 @@
         <v>0.073</v>
       </c>
       <c r="Q49" t="n">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="R49" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5225,10 +5225,10 @@
         <v>4.02</v>
       </c>
       <c r="AA49" t="n">
-        <v>92.06</v>
+        <v>91.7</v>
       </c>
       <c r="AB49" t="n">
-        <v>104.15</v>
+        <v>103.94</v>
       </c>
       <c r="AC49" t="n">
         <v>-25.9</v>
@@ -5314,17 +5314,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gandhar Oil Refinery (India) Limited</t>
+          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>257.72</v>
+        <v>261.8</v>
       </c>
       <c r="D2" t="n">
         <v>158.6</v>
       </c>
       <c r="E2" t="n">
-        <v>62.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>64.63</v>
@@ -5353,13 +5353,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90.58</v>
+        <v>90.44</v>
       </c>
       <c r="D3" t="n">
         <v>55.78</v>
       </c>
       <c r="E3" t="n">
-        <v>62.4</v>
+        <v>62.1</v>
       </c>
       <c r="F3" t="n">
         <v>67.45999999999999</v>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1989.3</v>
+        <v>1911.3</v>
       </c>
       <c r="D4" t="n">
         <v>920.51</v>
       </c>
       <c r="E4" t="n">
-        <v>116.1</v>
+        <v>107.6</v>
       </c>
       <c r="F4" t="n">
         <v>73.16</v>
@@ -5423,13 +5423,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>834.9</v>
+        <v>843.85</v>
       </c>
       <c r="D5" t="n">
         <v>745.6900000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>13.2</v>
       </c>
       <c r="F5" t="n">
         <v>69.61</v>
@@ -5458,13 +5458,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>250.68</v>
+        <v>263.2</v>
       </c>
       <c r="D6" t="n">
         <v>217.8</v>
       </c>
       <c r="E6" t="n">
-        <v>15.1</v>
+        <v>20.8</v>
       </c>
       <c r="F6" t="n">
         <v>71.75</v>
@@ -5484,70 +5484,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>THANGAMAIYL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>70.63</v>
+        <v>5311.5</v>
       </c>
       <c r="D7" t="n">
-        <v>70.34999999999999</v>
+        <v>5198.76</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="F7" t="n">
-        <v>72.56999999999999</v>
+        <v>67.16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.04</v>
+        <v>7.21</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5412</v>
+        <v>70.09</v>
       </c>
       <c r="D8" t="n">
-        <v>5187.29</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3</v>
+        <v>-0.4</v>
       </c>
       <c r="F8" t="n">
-        <v>67.16</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>6.71</v>
+        <v>1.04</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
     </row>
@@ -5563,13 +5563,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>256.53</v>
+        <v>267.6</v>
       </c>
       <c r="D9" t="n">
         <v>243.52</v>
       </c>
       <c r="E9" t="n">
-        <v>5.3</v>
+        <v>9.9</v>
       </c>
       <c r="F9" t="n">
         <v>67.65000000000001</v>
@@ -5598,13 +5598,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>536.55</v>
+        <v>511.25</v>
       </c>
       <c r="D10" t="n">
         <v>390.61</v>
       </c>
       <c r="E10" t="n">
-        <v>37.4</v>
+        <v>30.9</v>
       </c>
       <c r="F10" t="n">
         <v>63.09</v>
@@ -5624,140 +5624,140 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>191.8</v>
+        <v>374.55</v>
       </c>
       <c r="D11" t="n">
-        <v>164.1</v>
+        <v>338.1</v>
       </c>
       <c r="E11" t="n">
-        <v>16.9</v>
+        <v>10.8</v>
       </c>
       <c r="F11" t="n">
-        <v>60.6</v>
+        <v>66.73</v>
       </c>
       <c r="G11" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>SENCO GOLD LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>378.75</v>
+        <v>352.75</v>
       </c>
       <c r="D12" t="n">
-        <v>338.1</v>
+        <v>335.41</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="F12" t="n">
-        <v>66.73</v>
+        <v>68.48</v>
       </c>
       <c r="G12" t="n">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>331.8</v>
+        <v>190.05</v>
       </c>
       <c r="D13" t="n">
-        <v>314.32</v>
+        <v>164.1</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6</v>
+        <v>15.8</v>
       </c>
       <c r="F13" t="n">
-        <v>63.24</v>
+        <v>60.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.74</v>
+        <v>0.25</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NUPUR RECYCLERS LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>122.5</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>82.93000000000001</v>
+        <v>91.62</v>
       </c>
       <c r="E14" t="n">
-        <v>47.7</v>
+        <v>7.9</v>
       </c>
       <c r="F14" t="n">
-        <v>72.53</v>
+        <v>70.88</v>
       </c>
       <c r="G14" t="n">
-        <v>0.42</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
     </row>
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>661.2</v>
+        <v>623.1</v>
       </c>
       <c r="D15" t="n">
         <v>577.97</v>
       </c>
       <c r="E15" t="n">
-        <v>14.4</v>
+        <v>7.8</v>
       </c>
       <c r="F15" t="n">
         <v>64.68000000000001</v>
@@ -5799,70 +5799,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>501.55</v>
+        <v>339</v>
       </c>
       <c r="D16" t="n">
-        <v>476.81</v>
+        <v>314.32</v>
       </c>
       <c r="E16" t="n">
-        <v>5.2</v>
+        <v>7.9</v>
       </c>
       <c r="F16" t="n">
-        <v>62.09</v>
+        <v>63.24</v>
       </c>
       <c r="G16" t="n">
-        <v>0.57</v>
+        <v>1.74</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>NUPUR RECYCLERS LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>82.38</v>
+        <v>120.05</v>
       </c>
       <c r="D17" t="n">
-        <v>76.98</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>44.8</v>
       </c>
       <c r="F17" t="n">
-        <v>62.78</v>
+        <v>72.53</v>
       </c>
       <c r="G17" t="n">
-        <v>2.64</v>
+        <v>0.42</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
@@ -5878,13 +5878,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19.52</v>
+        <v>19.84</v>
       </c>
       <c r="D18" t="n">
         <v>21.01</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.1</v>
+        <v>-5.6</v>
       </c>
       <c r="F18" t="n">
         <v>70.87</v>
@@ -5904,140 +5904,140 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RGL</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Renaissance Global Limited</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>135.22</v>
+        <v>82.91</v>
       </c>
       <c r="D19" t="n">
-        <v>100.9</v>
+        <v>76.98</v>
       </c>
       <c r="E19" t="n">
-        <v>34</v>
+        <v>7.7</v>
       </c>
       <c r="F19" t="n">
-        <v>69.56</v>
+        <v>62.78</v>
       </c>
       <c r="G19" t="n">
-        <v>3.01</v>
+        <v>2.64</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>RGL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>Renaissance Global Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>98.73999999999999</v>
+        <v>136.96</v>
       </c>
       <c r="D20" t="n">
-        <v>89.34</v>
+        <v>100.9</v>
       </c>
       <c r="E20" t="n">
-        <v>10.5</v>
+        <v>35.7</v>
       </c>
       <c r="F20" t="n">
-        <v>70.88</v>
+        <v>69.56</v>
       </c>
       <c r="G20" t="n">
-        <v>6.25</v>
+        <v>3.01</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>DIAMONDYD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SENCO GOLD LIMITED</t>
+          <t>Prataap Snacks Limited</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>348.6</v>
+        <v>1144.8</v>
       </c>
       <c r="D21" t="n">
-        <v>335.41</v>
+        <v>1174.34</v>
       </c>
       <c r="E21" t="n">
-        <v>3.9</v>
+        <v>-2.5</v>
       </c>
       <c r="F21" t="n">
-        <v>68.48</v>
+        <v>69.75</v>
       </c>
       <c r="G21" t="n">
-        <v>0.41</v>
+        <v>65.58</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DIAMONDYD</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Prataap Snacks Limited</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1147.1</v>
+        <v>494.45</v>
       </c>
       <c r="D22" t="n">
-        <v>1174.34</v>
+        <v>479.69</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3</v>
+        <v>3.1</v>
       </c>
       <c r="F22" t="n">
-        <v>69.75</v>
+        <v>62.09</v>
       </c>
       <c r="G22" t="n">
-        <v>65.58</v>
+        <v>0.66</v>
       </c>
       <c r="H22" t="n">
         <v>5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.04</v>
+        <v>28.03</v>
       </c>
       <c r="D23" t="n">
         <v>29.14</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1312.2</v>
+        <v>1351.4</v>
       </c>
       <c r="D24" t="n">
         <v>1104.34</v>
       </c>
       <c r="E24" t="n">
-        <v>18.8</v>
+        <v>22.4</v>
       </c>
       <c r="F24" t="n">
         <v>60.82</v>
@@ -6114,175 +6114,175 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>13.79</v>
+        <v>124.56</v>
       </c>
       <c r="D25" t="n">
-        <v>12.34</v>
+        <v>105.19</v>
       </c>
       <c r="E25" t="n">
-        <v>11.8</v>
+        <v>18.4</v>
       </c>
       <c r="F25" t="n">
-        <v>69.12</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>1.38</v>
+        <v>2.63</v>
       </c>
       <c r="H25" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>122.62</v>
+        <v>168.2</v>
       </c>
       <c r="D26" t="n">
-        <v>105.19</v>
+        <v>201.21</v>
       </c>
       <c r="E26" t="n">
-        <v>16.6</v>
+        <v>-16.4</v>
       </c>
       <c r="F26" t="n">
-        <v>67.15000000000001</v>
+        <v>64.08</v>
       </c>
       <c r="G26" t="n">
-        <v>2.63</v>
+        <v>8.07</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>THOMAS COOK (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>171.15</v>
+        <v>105.71</v>
       </c>
       <c r="D27" t="n">
-        <v>201.21</v>
+        <v>109.31</v>
       </c>
       <c r="E27" t="n">
-        <v>-14.9</v>
+        <v>-3.3</v>
       </c>
       <c r="F27" t="n">
-        <v>64.08</v>
+        <v>72.34</v>
       </c>
       <c r="G27" t="n">
-        <v>8.07</v>
+        <v>48.4</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>THOMAS COOK (INDIA) LIMITED</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>107.92</v>
+        <v>508.8</v>
       </c>
       <c r="D28" t="n">
-        <v>109.31</v>
+        <v>545.03</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.3</v>
+        <v>-6.6</v>
       </c>
       <c r="F28" t="n">
-        <v>72.34</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>48.4</v>
+        <v>1.09</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>BAJAJHCARE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>BAJAJ HEALTHCARE LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>508.75</v>
+        <v>329</v>
       </c>
       <c r="D29" t="n">
-        <v>545.03</v>
+        <v>297.3</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.7</v>
+        <v>10.7</v>
       </c>
       <c r="F29" t="n">
-        <v>69.90000000000001</v>
+        <v>67.69</v>
       </c>
       <c r="G29" t="n">
-        <v>1.09</v>
+        <v>2.97</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
     </row>
@@ -6298,96 +6298,96 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>209.94</v>
+        <v>207.76</v>
       </c>
       <c r="D30" t="n">
-        <v>209.98</v>
+        <v>210.35</v>
       </c>
       <c r="E30" t="n">
-        <v>-0</v>
+        <v>-1.2</v>
       </c>
       <c r="F30" t="n">
         <v>67.04000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BAJAJ HEALTHCARE LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>333.7</v>
+        <v>171.12</v>
       </c>
       <c r="D31" t="n">
-        <v>297.3</v>
+        <v>175.74</v>
       </c>
       <c r="E31" t="n">
-        <v>12.2</v>
+        <v>-2.6</v>
       </c>
       <c r="F31" t="n">
-        <v>67.69</v>
+        <v>74.59</v>
       </c>
       <c r="G31" t="n">
-        <v>2.97</v>
+        <v>0.49</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>172.27</v>
+        <v>13.34</v>
       </c>
       <c r="D32" t="n">
-        <v>180.98</v>
+        <v>12.4</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.8</v>
+        <v>7.6</v>
       </c>
       <c r="F32" t="n">
-        <v>74.59</v>
+        <v>69.12</v>
       </c>
       <c r="G32" t="n">
-        <v>0.25</v>
+        <v>1.46</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
@@ -6403,13 +6403,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>263.7</v>
+        <v>259.35</v>
       </c>
       <c r="D33" t="n">
         <v>257.65</v>
       </c>
       <c r="E33" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="F33" t="n">
         <v>70.09</v>
@@ -6429,70 +6429,70 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>746</v>
+        <v>55.04</v>
       </c>
       <c r="D34" t="n">
-        <v>717.77</v>
+        <v>53.49</v>
       </c>
       <c r="E34" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="F34" t="n">
-        <v>61.71</v>
+        <v>67.23</v>
       </c>
       <c r="G34" t="n">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>174.16</v>
+        <v>739.5</v>
       </c>
       <c r="D35" t="n">
-        <v>182.69</v>
+        <v>717.77</v>
       </c>
       <c r="E35" t="n">
-        <v>-4.7</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>69.05</v>
+        <v>61.71</v>
       </c>
       <c r="G35" t="n">
-        <v>0.74</v>
+        <v>1.61</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
     </row>
@@ -6508,13 +6508,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>116.9</v>
+        <v>115.67</v>
       </c>
       <c r="D36" t="n">
         <v>114.86</v>
       </c>
       <c r="E36" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="F36" t="n">
         <v>69.73999999999999</v>
@@ -6534,245 +6534,245 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>268.95</v>
+        <v>740.55</v>
       </c>
       <c r="D37" t="n">
-        <v>269.7</v>
+        <v>815.16</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.3</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>73.09</v>
+        <v>73.2</v>
       </c>
       <c r="G37" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>41.65</v>
+        <v>428.15</v>
       </c>
       <c r="D38" t="n">
-        <v>43.04</v>
+        <v>474.82</v>
       </c>
       <c r="E38" t="n">
-        <v>-3.2</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>71.79000000000001</v>
+        <v>70.55</v>
       </c>
       <c r="G38" t="n">
-        <v>1.02</v>
+        <v>10.22</v>
       </c>
       <c r="H38" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>727.55</v>
+        <v>169.08</v>
       </c>
       <c r="D39" t="n">
-        <v>815.16</v>
+        <v>182.69</v>
       </c>
       <c r="E39" t="n">
-        <v>-10.7</v>
+        <v>-7.4</v>
       </c>
       <c r="F39" t="n">
-        <v>73.2</v>
+        <v>69.05</v>
       </c>
       <c r="G39" t="n">
-        <v>1.24</v>
+        <v>0.74</v>
       </c>
       <c r="H39" t="n">
         <v>3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>429.6</v>
+        <v>111.83</v>
       </c>
       <c r="D40" t="n">
-        <v>474.82</v>
+        <v>113.5</v>
       </c>
       <c r="E40" t="n">
-        <v>-9.5</v>
+        <v>-1.5</v>
       </c>
       <c r="F40" t="n">
-        <v>70.55</v>
+        <v>73.48</v>
       </c>
       <c r="G40" t="n">
-        <v>10.22</v>
+        <v>0.6</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>54.82</v>
+        <v>55.28</v>
       </c>
       <c r="D41" t="n">
-        <v>53.49</v>
+        <v>60.15</v>
       </c>
       <c r="E41" t="n">
-        <v>2.5</v>
+        <v>-8.1</v>
       </c>
       <c r="F41" t="n">
-        <v>67.23</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>1.99</v>
+        <v>0.9</v>
       </c>
       <c r="H41" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>67.40000000000001</v>
+        <v>266.6</v>
       </c>
       <c r="D42" t="n">
-        <v>64.04000000000001</v>
+        <v>269.7</v>
       </c>
       <c r="E42" t="n">
-        <v>5.2</v>
+        <v>-1.1</v>
       </c>
       <c r="F42" t="n">
-        <v>64.29000000000001</v>
+        <v>73.09</v>
       </c>
       <c r="G42" t="n">
-        <v>0.31</v>
+        <v>1.48</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>56.57</v>
+        <v>41.53</v>
       </c>
       <c r="D43" t="n">
-        <v>60.15</v>
+        <v>43.04</v>
       </c>
       <c r="E43" t="n">
-        <v>-6</v>
+        <v>-3.5</v>
       </c>
       <c r="F43" t="n">
-        <v>73.01000000000001</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
     </row>
@@ -6788,13 +6788,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>86.47</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="D44" t="n">
         <v>95.54000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>-9.5</v>
+        <v>-10.7</v>
       </c>
       <c r="F44" t="n">
         <v>71.72</v>
@@ -6823,13 +6823,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>173.61</v>
+        <v>173.3</v>
       </c>
       <c r="D45" t="n">
         <v>173.91</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="F45" t="n">
         <v>65.64</v>
@@ -6849,105 +6849,105 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>MBEL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>M &amp; B Engineering Limited</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>111.85</v>
+        <v>265.6</v>
       </c>
       <c r="D46" t="n">
-        <v>114.25</v>
+        <v>292.28</v>
       </c>
       <c r="E46" t="n">
-        <v>-2.1</v>
+        <v>-9.1</v>
       </c>
       <c r="F46" t="n">
-        <v>73.48</v>
+        <v>70.45</v>
       </c>
       <c r="G46" t="n">
-        <v>0.43</v>
+        <v>1.29</v>
       </c>
       <c r="H46" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MBEL</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>M &amp; B Engineering Limited</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>267.25</v>
+        <v>28.15</v>
       </c>
       <c r="D47" t="n">
-        <v>292.28</v>
+        <v>34.54</v>
       </c>
       <c r="E47" t="n">
-        <v>-8.6</v>
+        <v>-18.5</v>
       </c>
       <c r="F47" t="n">
-        <v>70.45</v>
+        <v>61.81</v>
       </c>
       <c r="G47" t="n">
-        <v>1.29</v>
+        <v>0.88</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>28.26</v>
+        <v>66.19</v>
       </c>
       <c r="D48" t="n">
-        <v>34.54</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>-18.2</v>
+        <v>3.4</v>
       </c>
       <c r="F48" t="n">
-        <v>61.81</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>0.88</v>
+        <v>0.31</v>
       </c>
       <c r="H48" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
     </row>
@@ -6963,13 +6963,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>84.01000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D49" t="n">
         <v>100.33</v>
       </c>
       <c r="E49" t="n">
-        <v>-16.3</v>
+        <v>-15.4</v>
       </c>
       <c r="F49" t="n">
         <v>71.89</v>
@@ -7019,7 +7019,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -7089,7 +7089,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/output/2026-09-01/enriched_analysis.xlsx
+++ b/output/2026-09-01/enriched_analysis.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.078</v>
+        <v>0.076</v>
       </c>
       <c r="Q2" t="n">
-        <v>2561</v>
+        <v>2604</v>
       </c>
       <c r="R2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>36</v>
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.652</v>
+        <v>0.664</v>
       </c>
       <c r="Q3" t="n">
-        <v>950</v>
+        <v>932</v>
       </c>
       <c r="R3" t="n">
-        <v>27.2</v>
+        <v>26.7</v>
       </c>
       <c r="S3" t="n">
         <v>19</v>
@@ -805,16 +805,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MACPOWER CNC MACHINES LIMITED</t>
+          <t>Alembic Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -834,80 +834,80 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1911.3</v>
+        <v>843.85</v>
       </c>
       <c r="J4" t="n">
-        <v>920.51</v>
+        <v>746.02</v>
       </c>
       <c r="K4" t="n">
-        <v>107.6</v>
+        <v>13.1</v>
       </c>
       <c r="L4" t="n">
-        <v>73.16</v>
+        <v>69.61</v>
       </c>
       <c r="M4" t="n">
-        <v>0.44</v>
+        <v>7.69</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.023</v>
+        <v>0.047</v>
       </c>
       <c r="Q4" t="n">
-        <v>1912</v>
+        <v>16287</v>
       </c>
       <c r="R4" t="n">
-        <v>49.2</v>
+        <v>20.7</v>
       </c>
       <c r="S4" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="T4" t="n">
-        <v>15.42</v>
+        <v>346</v>
       </c>
       <c r="U4" t="n">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="V4" t="n">
-        <v>9.58</v>
+        <v>10.02</v>
       </c>
       <c r="W4" t="n">
-        <v>29.1</v>
+        <v>12.3</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="Y4" t="b">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.19</v>
+        <v>19</v>
       </c>
       <c r="AA4" t="n">
-        <v>1542.98</v>
+        <v>819.41</v>
       </c>
       <c r="AB4" t="n">
-        <v>1121.56</v>
+        <v>791.49</v>
       </c>
       <c r="AC4" t="n">
-        <v>92.90000000000001</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Limited</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -931,84 +931,84 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>843.85</v>
+        <v>263.2</v>
       </c>
       <c r="J5" t="n">
-        <v>745.6900000000001</v>
+        <v>217.8</v>
       </c>
       <c r="K5" t="n">
-        <v>13.2</v>
+        <v>20.8</v>
       </c>
       <c r="L5" t="n">
-        <v>69.61</v>
+        <v>71.75</v>
       </c>
       <c r="M5" t="n">
-        <v>9.18</v>
+        <v>0.82</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.055</v>
+        <v>0.068</v>
       </c>
       <c r="Q5" t="n">
-        <v>16568</v>
+        <v>1200</v>
       </c>
       <c r="R5" t="n">
-        <v>21</v>
+        <v>16.2</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="T5" t="n">
-        <v>346</v>
+        <v>40</v>
       </c>
       <c r="U5" t="n">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="V5" t="n">
-        <v>10.02</v>
+        <v>8.23</v>
       </c>
       <c r="W5" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="X5" t="n">
-        <v>0.21</v>
+        <v>0.01</v>
       </c>
       <c r="Y5" t="b">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>819.41</v>
+        <v>214.79</v>
       </c>
       <c r="AB5" t="n">
-        <v>791.49</v>
+        <v>181.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>THANGAMAIYL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1019,93 +1019,93 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>263.2</v>
+        <v>5311.5</v>
       </c>
       <c r="J6" t="n">
-        <v>217.8</v>
+        <v>5198.76</v>
       </c>
       <c r="K6" t="n">
-        <v>20.8</v>
+        <v>2.2</v>
       </c>
       <c r="L6" t="n">
-        <v>71.75</v>
+        <v>67.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0.82</v>
+        <v>7.21</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.044</v>
       </c>
       <c r="Q6" t="n">
-        <v>1154</v>
+        <v>16334</v>
       </c>
       <c r="R6" t="n">
-        <v>15.6</v>
+        <v>41.6</v>
       </c>
       <c r="S6" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="T6" t="n">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="U6" t="n">
-        <v>54</v>
+        <v>264</v>
       </c>
       <c r="V6" t="n">
-        <v>8.23</v>
+        <v>27.38</v>
       </c>
       <c r="W6" t="n">
-        <v>11</v>
+        <v>25.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01</v>
+        <v>0.64</v>
       </c>
       <c r="Y6" t="b">
         <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>214.79</v>
+        <v>5877.56</v>
       </c>
       <c r="AB6" t="n">
-        <v>181.32</v>
+        <v>4295.56</v>
       </c>
       <c r="AC6" t="n">
-        <v>69.7</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>THANGAMAIYL JEWELLERY LIMITED</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
         <v>20</v>
@@ -1125,95 +1125,95 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>5311.5</v>
+        <v>70.09</v>
       </c>
       <c r="J7" t="n">
-        <v>5198.76</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2</v>
+        <v>-0.4</v>
       </c>
       <c r="L7" t="n">
-        <v>67.16</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>7.21</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.044</v>
+        <v>0.495</v>
       </c>
       <c r="Q7" t="n">
-        <v>16512</v>
+        <v>210</v>
       </c>
       <c r="R7" t="n">
-        <v>42</v>
+        <v>8.94</v>
       </c>
       <c r="S7" t="n">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="T7" t="n">
-        <v>145</v>
+        <v>27.97</v>
       </c>
       <c r="U7" t="n">
-        <v>264</v>
+        <v>17</v>
       </c>
       <c r="V7" t="n">
-        <v>27.38</v>
+        <v>2.73</v>
       </c>
       <c r="W7" t="n">
-        <v>25.5</v>
+        <v>13.7</v>
       </c>
       <c r="X7" t="n">
-        <v>0.64</v>
+        <v>1.86</v>
       </c>
       <c r="Y7" t="b">
         <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>5877.56</v>
+        <v>56.41</v>
       </c>
       <c r="AB7" t="n">
-        <v>4295.56</v>
+        <v>51.46</v>
       </c>
       <c r="AC7" t="n">
-        <v>38.6</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Strong Buy Setup</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -1222,69 +1222,67 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>70.09</v>
+        <v>511.25</v>
       </c>
       <c r="J8" t="n">
-        <v>70.34999999999999</v>
+        <v>390.61</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4</v>
+        <v>30.9</v>
       </c>
       <c r="L8" t="n">
-        <v>72.56999999999999</v>
+        <v>63.09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>8.02</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.51</v>
+        <v>0.489</v>
       </c>
       <c r="Q8" t="n">
-        <v>204</v>
+        <v>1641</v>
       </c>
       <c r="R8" t="n">
-        <v>8.69</v>
+        <v>19.4</v>
       </c>
       <c r="S8" t="n">
-        <v>17</v>
+        <v>581</v>
       </c>
       <c r="T8" t="n">
-        <v>27.97</v>
+        <v>34</v>
       </c>
       <c r="U8" t="n">
-        <v>17</v>
+        <v>881</v>
       </c>
       <c r="V8" t="n">
-        <v>2.73</v>
+        <v>8.58</v>
       </c>
       <c r="W8" t="n">
-        <v>13.7</v>
+        <v>22</v>
       </c>
       <c r="X8" t="n">
-        <v>1.86</v>
+        <v>0.33</v>
       </c>
       <c r="Y8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.140000000000001</v>
+        <v>29</v>
       </c>
       <c r="AA8" t="n">
-        <v>56.41</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>51.46</v>
-      </c>
+        <v>468.45</v>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>53.6</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="9">
@@ -1299,11 +1297,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Strong Buy Setup</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1316,7 +1314,7 @@
         <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="I9" t="n">
         <v>267.6</v>
@@ -1342,13 +1340,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.157</v>
+        <v>0.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>705</v>
+        <v>742</v>
       </c>
       <c r="R9" t="n">
-        <v>58.9</v>
+        <v>62</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1387,16 +1385,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,79 +1402,79 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>511.25</v>
+        <v>190.05</v>
       </c>
       <c r="J10" t="n">
-        <v>390.61</v>
+        <v>164.1</v>
       </c>
       <c r="K10" t="n">
-        <v>30.9</v>
+        <v>15.8</v>
       </c>
       <c r="L10" t="n">
-        <v>63.09</v>
+        <v>60.6</v>
       </c>
       <c r="M10" t="n">
-        <v>8.02</v>
+        <v>0.25</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.494</v>
+        <v>0.006</v>
       </c>
       <c r="Q10" t="n">
-        <v>1624</v>
-      </c>
-      <c r="R10" t="n">
-        <v>19.2</v>
-      </c>
+        <v>4026</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>581</v>
+        <v>39</v>
       </c>
       <c r="T10" t="n">
-        <v>34</v>
+        <v>258</v>
       </c>
       <c r="U10" t="n">
-        <v>881</v>
+        <v>30</v>
       </c>
       <c r="V10" t="n">
-        <v>8.58</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>22</v>
+        <v>6.38</v>
       </c>
       <c r="X10" t="n">
-        <v>0.33</v>
+        <v>10.11</v>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="AA10" t="n">
-        <v>468.45</v>
-      </c>
-      <c r="AB10" t="inlineStr"/>
+        <v>177.86</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>178.69</v>
+      </c>
       <c r="AC10" t="n">
-        <v>24.2</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1534,13 +1532,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.077</v>
+        <v>0.078</v>
       </c>
       <c r="Q11" t="n">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="R11" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S11" t="n">
         <v>-8</v>
@@ -1634,10 +1632,10 @@
         <v>0.007</v>
       </c>
       <c r="Q12" t="n">
-        <v>5779</v>
+        <v>5638</v>
       </c>
       <c r="R12" t="n">
-        <v>9.77</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>43</v>
@@ -1676,12 +1674,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1693,10 +1691,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
         <v>25</v>
@@ -1705,78 +1703,80 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>190.05</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>164.1</v>
+        <v>91.62</v>
       </c>
       <c r="K13" t="n">
-        <v>15.8</v>
+        <v>7.9</v>
       </c>
       <c r="L13" t="n">
-        <v>60.6</v>
+        <v>70.88</v>
       </c>
       <c r="M13" t="n">
-        <v>0.25</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.006</v>
+        <v>0.328</v>
       </c>
       <c r="Q13" t="n">
-        <v>4021</v>
-      </c>
-      <c r="R13" t="inlineStr"/>
+        <v>2555</v>
+      </c>
+      <c r="R13" t="n">
+        <v>20.9</v>
+      </c>
       <c r="S13" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>258</v>
+        <v>14</v>
       </c>
       <c r="U13" t="n">
-        <v>30</v>
+        <v>-14</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.13</v>
+        <v>0.57</v>
       </c>
       <c r="W13" t="n">
-        <v>6.38</v>
+        <v>16.9</v>
       </c>
       <c r="X13" t="n">
-        <v>10.11</v>
+        <v>0.01</v>
       </c>
       <c r="Y13" t="b">
         <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="AA13" t="n">
-        <v>177.86</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>178.69</v>
+        <v>92</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1788,96 +1788,96 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>623.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>577.97</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>40</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>27-08-2026</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1118</v>
+      </c>
+      <c r="R14" t="n">
+        <v>57</v>
+      </c>
+      <c r="S14" t="n">
+        <v>21</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="U14" t="n">
+        <v>23</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y14" t="b">
         <v>0</v>
       </c>
-      <c r="I14" t="n">
-        <v>98.84999999999999</v>
-      </c>
-      <c r="J14" t="n">
-        <v>91.62</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="L14" t="n">
-        <v>70.88</v>
-      </c>
-      <c r="M14" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>01-09-2026</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2535</v>
-      </c>
-      <c r="R14" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S14" t="n">
-        <v>8</v>
-      </c>
-      <c r="T14" t="n">
-        <v>14</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-14</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="W14" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Y14" t="b">
-        <v>1</v>
-      </c>
       <c r="Z14" t="n">
-        <v>30</v>
+        <v>-110</v>
       </c>
       <c r="AA14" t="n">
-        <v>90.59999999999999</v>
+        <v>573.96</v>
       </c>
       <c r="AB14" t="n">
-        <v>92</v>
+        <v>506.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.3</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1894,87 +1894,87 @@
         <v>30</v>
       </c>
       <c r="H15" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I15" t="n">
-        <v>623.1</v>
+        <v>339</v>
       </c>
       <c r="J15" t="n">
-        <v>577.97</v>
+        <v>314.32</v>
       </c>
       <c r="K15" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="L15" t="n">
-        <v>64.68000000000001</v>
+        <v>63.24</v>
       </c>
       <c r="M15" t="n">
-        <v>5.8</v>
+        <v>1.74</v>
       </c>
       <c r="N15" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.504</v>
+        <v>0.544</v>
       </c>
       <c r="Q15" t="n">
-        <v>1150</v>
+        <v>320</v>
       </c>
       <c r="R15" t="n">
-        <v>58.6</v>
+        <v>147</v>
       </c>
       <c r="S15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.11</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>23</v>
+        <v>264</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>2.55</v>
       </c>
       <c r="W15" t="n">
-        <v>1.58</v>
+        <v>2.07</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Y15" t="b">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>-110</v>
+        <v>6.06</v>
       </c>
       <c r="AA15" t="n">
-        <v>573.96</v>
+        <v>293.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>506.88</v>
+        <v>277.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>27.3</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>NUPUR RECYCLERS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1985,93 +1985,93 @@
         <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
       </c>
       <c r="H16" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="I16" t="n">
-        <v>339</v>
+        <v>120.05</v>
       </c>
       <c r="J16" t="n">
-        <v>314.32</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>7.9</v>
+        <v>44.8</v>
       </c>
       <c r="L16" t="n">
-        <v>63.24</v>
+        <v>72.53</v>
       </c>
       <c r="M16" t="n">
-        <v>1.74</v>
+        <v>0.42</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.544</v>
+        <v>0.051</v>
       </c>
       <c r="Q16" t="n">
-        <v>320</v>
+        <v>829</v>
       </c>
       <c r="R16" t="n">
-        <v>148</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>1.43</v>
       </c>
       <c r="U16" t="n">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="V16" t="n">
-        <v>2.55</v>
+        <v>0.34</v>
       </c>
       <c r="W16" t="n">
-        <v>2.07</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.06</v>
+        <v>3.67</v>
       </c>
       <c r="AA16" t="n">
-        <v>293.83</v>
+        <v>107.01</v>
       </c>
       <c r="AB16" t="n">
-        <v>277.03</v>
+        <v>69.69</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.5</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NUPUR RECYCLERS LIMITED</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2082,89 +2082,85 @@
         <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>120.05</v>
+        <v>19.84</v>
       </c>
       <c r="J17" t="n">
-        <v>82.93000000000001</v>
+        <v>21.01</v>
       </c>
       <c r="K17" t="n">
-        <v>44.8</v>
+        <v>-5.6</v>
       </c>
       <c r="L17" t="n">
-        <v>72.53</v>
+        <v>70.87</v>
       </c>
       <c r="M17" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="N17" t="n">
         <v>3</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.051</v>
+        <v>0.136</v>
       </c>
       <c r="Q17" t="n">
-        <v>829</v>
+        <v>367</v>
       </c>
       <c r="R17" t="n">
-        <v>88.59999999999999</v>
+        <v>5.93</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.43</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="V17" t="n">
-        <v>0.34</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>9.710000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="X17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Y17" t="b">
         <v>0</v>
       </c>
-      <c r="Y17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.67</v>
-      </c>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
-        <v>107.01</v>
+        <v>18.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>69.69</v>
+        <v>15.11</v>
       </c>
       <c r="AC17" t="n">
-        <v>131.2</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2179,89 +2175,93 @@
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>19.84</v>
+        <v>82.91</v>
       </c>
       <c r="J18" t="n">
-        <v>21.01</v>
+        <v>76.98</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.6</v>
+        <v>7.7</v>
       </c>
       <c r="L18" t="n">
-        <v>70.87</v>
+        <v>62.78</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5</v>
+        <v>2.64</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.133</v>
+        <v>0.623</v>
       </c>
       <c r="Q18" t="n">
-        <v>377</v>
+        <v>424</v>
       </c>
       <c r="R18" t="n">
-        <v>6.09</v>
+        <v>39.4</v>
       </c>
       <c r="S18" t="n">
-        <v>118</v>
-      </c>
-      <c r="T18" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8.390000000000001</v>
+      </c>
       <c r="U18" t="n">
-        <v>391</v>
+        <v>-19</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="W18" t="n">
-        <v>18.5</v>
+        <v>8.73</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01</v>
+        <v>0.28</v>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>41.64</v>
+      </c>
       <c r="AA18" t="n">
-        <v>18.1</v>
+        <v>75.88</v>
       </c>
       <c r="AB18" t="n">
-        <v>15.11</v>
+        <v>78.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>39.7</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>RGL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>Renaissance Global Limited</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2269,96 +2269,96 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>82.91</v>
+        <v>136.96</v>
       </c>
       <c r="J19" t="n">
-        <v>76.98</v>
+        <v>100.9</v>
       </c>
       <c r="K19" t="n">
-        <v>7.7</v>
+        <v>35.7</v>
       </c>
       <c r="L19" t="n">
-        <v>62.78</v>
+        <v>69.56</v>
       </c>
       <c r="M19" t="n">
-        <v>2.64</v>
+        <v>3.01</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.617</v>
+        <v>0.204</v>
       </c>
       <c r="Q19" t="n">
-        <v>428</v>
+        <v>1474</v>
       </c>
       <c r="R19" t="n">
-        <v>39.7</v>
+        <v>51.4</v>
       </c>
       <c r="S19" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="T19" t="n">
-        <v>8.390000000000001</v>
+        <v>22</v>
       </c>
       <c r="U19" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.54</v>
+        <v>0.95</v>
       </c>
       <c r="W19" t="n">
-        <v>8.73</v>
+        <v>5.28</v>
       </c>
       <c r="X19" t="n">
-        <v>0.28</v>
+        <v>0.52</v>
       </c>
       <c r="Y19" t="b">
         <v>1</v>
       </c>
       <c r="Z19" t="n">
-        <v>41.64</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>75.88</v>
+        <v>121.96</v>
       </c>
       <c r="AB19" t="n">
-        <v>78.28</v>
+        <v>115.45</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RGL</t>
+          <t>DIAMONDYD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Renaissance Global Limited</t>
+          <t>Prataap Snacks Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2366,96 +2366,96 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="I20" t="n">
-        <v>136.96</v>
+        <v>1144.8</v>
       </c>
       <c r="J20" t="n">
-        <v>100.9</v>
+        <v>1174.34</v>
       </c>
       <c r="K20" t="n">
-        <v>35.7</v>
+        <v>-2.5</v>
       </c>
       <c r="L20" t="n">
-        <v>69.56</v>
+        <v>69.75</v>
       </c>
       <c r="M20" t="n">
-        <v>3.01</v>
+        <v>65.58</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.205</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>1470</v>
+        <v>2756</v>
       </c>
       <c r="R20" t="n">
-        <v>51.3</v>
+        <v>216</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>22</v>
+        <v>19.05</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="V20" t="n">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>5.28</v>
+        <v>3.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>3.87</v>
       </c>
       <c r="AA20" t="n">
-        <v>121.96</v>
+        <v>1165.18</v>
       </c>
       <c r="AB20" t="n">
-        <v>115.45</v>
+        <v>1085.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DIAMONDYD</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Prataap Snacks Limited</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,96 +2463,96 @@
         </is>
       </c>
       <c r="E21" t="n">
+        <v>15</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14</v>
+      </c>
+      <c r="G21" t="n">
         <v>25</v>
       </c>
-      <c r="F21" t="n">
-        <v>21</v>
-      </c>
-      <c r="G21" t="n">
-        <v>15</v>
-      </c>
       <c r="H21" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1144.8</v>
+        <v>494.45</v>
       </c>
       <c r="J21" t="n">
-        <v>1174.34</v>
+        <v>479.69</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.5</v>
+        <v>3.1</v>
       </c>
       <c r="L21" t="n">
-        <v>69.75</v>
+        <v>62.09</v>
       </c>
       <c r="M21" t="n">
-        <v>65.58</v>
+        <v>0.66</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.393</v>
+        <v>0.078</v>
       </c>
       <c r="Q21" t="n">
-        <v>2741</v>
+        <v>850</v>
       </c>
       <c r="R21" t="n">
-        <v>215</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>19.05</v>
+        <v>30</v>
       </c>
       <c r="U21" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>14.66</v>
       </c>
       <c r="W21" t="n">
-        <v>3.08</v>
+        <v>14.4</v>
       </c>
       <c r="X21" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="Y21" t="b">
         <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.87</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>1165.18</v>
+        <v>489.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1085.15</v>
+        <v>488.67</v>
       </c>
       <c r="AC21" t="n">
-        <v>6.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2560,92 +2560,92 @@
         </is>
       </c>
       <c r="E22" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="J22" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N22" t="n">
         <v>15</v>
       </c>
-      <c r="F22" t="n">
-        <v>14</v>
-      </c>
-      <c r="G22" t="n">
-        <v>25</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>108</v>
+      </c>
+      <c r="R22" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>26</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="X22" t="n">
         <v>0</v>
       </c>
-      <c r="I22" t="n">
-        <v>494.45</v>
-      </c>
-      <c r="J22" t="n">
-        <v>479.69</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>62.09</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>01-09-2026</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>849</v>
-      </c>
-      <c r="R22" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="S22" t="n">
-        <v>7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>30</v>
-      </c>
-      <c r="U22" t="n">
+      <c r="Y22" t="b">
         <v>0</v>
       </c>
-      <c r="V22" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="W22" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Y22" t="b">
-        <v>1</v>
-      </c>
       <c r="Z22" t="n">
-        <v>14</v>
+        <v>21.51</v>
       </c>
       <c r="AA22" t="n">
-        <v>489.15</v>
+        <v>27.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>488.67</v>
+        <v>24.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.6</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2657,96 +2657,96 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F23" t="n">
+        <v>30</v>
+      </c>
+      <c r="G23" t="n">
         <v>10</v>
       </c>
-      <c r="G23" t="n">
-        <v>20</v>
-      </c>
       <c r="H23" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>28.03</v>
+        <v>1351.4</v>
       </c>
       <c r="J23" t="n">
-        <v>29.14</v>
+        <v>1104.34</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.8</v>
+        <v>22.4</v>
       </c>
       <c r="L23" t="n">
-        <v>69.03</v>
+        <v>60.82</v>
       </c>
       <c r="M23" t="n">
-        <v>1.34</v>
+        <v>5.22</v>
       </c>
       <c r="N23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.207</v>
+        <v>0.001</v>
       </c>
       <c r="Q23" t="n">
-        <v>111</v>
+        <v>361189</v>
       </c>
       <c r="R23" t="n">
-        <v>79.59999999999999</v>
+        <v>19.9</v>
       </c>
       <c r="S23" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4</v>
+        <v>4158</v>
       </c>
       <c r="U23" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="V23" t="n">
-        <v>0.59</v>
+        <v>25.89</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.18</v>
+        <v>53.4</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="Y23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.51</v>
+        <v>29</v>
       </c>
       <c r="AA23" t="n">
-        <v>27.33</v>
+        <v>1254.09</v>
       </c>
       <c r="AB23" t="n">
-        <v>24.62</v>
+        <v>1394.31</v>
       </c>
       <c r="AC23" t="n">
-        <v>34.8</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2754,96 +2754,96 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1351.4</v>
+        <v>124.56</v>
       </c>
       <c r="J24" t="n">
-        <v>1104.34</v>
+        <v>105.19</v>
       </c>
       <c r="K24" t="n">
-        <v>22.4</v>
+        <v>18.4</v>
       </c>
       <c r="L24" t="n">
-        <v>60.82</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>5.22</v>
+        <v>2.63</v>
       </c>
       <c r="N24" t="n">
         <v>1</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.001</v>
+        <v>0.053</v>
       </c>
       <c r="Q24" t="n">
-        <v>367621</v>
+        <v>4933</v>
       </c>
       <c r="R24" t="n">
-        <v>20.2</v>
+        <v>32.2</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>-25</v>
       </c>
       <c r="T24" t="n">
-        <v>4158</v>
+        <v>71</v>
       </c>
       <c r="U24" t="n">
-        <v>44</v>
+        <v>-11</v>
       </c>
       <c r="V24" t="n">
-        <v>25.89</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>53.4</v>
+        <v>10.7</v>
       </c>
       <c r="X24" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="Y24" t="b">
         <v>1</v>
       </c>
       <c r="Z24" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="AA24" t="n">
-        <v>1254.09</v>
+        <v>106.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>1394.31</v>
+        <v>112.27</v>
       </c>
       <c r="AC24" t="n">
-        <v>-1.9</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2851,189 +2851,189 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>124.56</v>
+        <v>168.2</v>
       </c>
       <c r="J25" t="n">
-        <v>105.19</v>
+        <v>201.21</v>
       </c>
       <c r="K25" t="n">
-        <v>18.4</v>
+        <v>-16.4</v>
       </c>
       <c r="L25" t="n">
-        <v>67.15000000000001</v>
+        <v>64.08</v>
       </c>
       <c r="M25" t="n">
-        <v>2.63</v>
+        <v>8.07</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.052</v>
+        <v>1.192</v>
       </c>
       <c r="Q25" t="n">
-        <v>5034</v>
+        <v>677</v>
       </c>
       <c r="R25" t="n">
-        <v>32.8</v>
+        <v>14.9</v>
       </c>
       <c r="S25" t="n">
-        <v>-25</v>
+        <v>-1</v>
       </c>
       <c r="T25" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="U25" t="n">
-        <v>-11</v>
+        <v>45</v>
       </c>
       <c r="V25" t="n">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="W25" t="n">
-        <v>10.7</v>
+        <v>19.4</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="AA25" t="n">
-        <v>106.06</v>
+        <v>176.27</v>
       </c>
       <c r="AB25" t="n">
-        <v>112.27</v>
+        <v>199.59</v>
       </c>
       <c r="AC25" t="n">
-        <v>17.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>THOMAS COOK (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Buy on Breakout</t>
+          <t>Watchlist</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>168.2</v>
+        <v>105.71</v>
       </c>
       <c r="J26" t="n">
-        <v>201.21</v>
+        <v>109.31</v>
       </c>
       <c r="K26" t="n">
-        <v>-16.4</v>
+        <v>-3.3</v>
       </c>
       <c r="L26" t="n">
-        <v>64.08</v>
+        <v>72.34</v>
       </c>
       <c r="M26" t="n">
-        <v>8.07</v>
+        <v>48.4</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.189</v>
+        <v>0.982</v>
       </c>
       <c r="Q26" t="n">
-        <v>679</v>
+        <v>4930</v>
       </c>
       <c r="R26" t="n">
-        <v>15</v>
+        <v>39.5</v>
       </c>
       <c r="S26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="U26" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="V26" t="n">
-        <v>3.1</v>
+        <v>1.25</v>
       </c>
       <c r="W26" t="n">
-        <v>19.4</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="Y26" t="b">
         <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA26" t="n">
-        <v>176.27</v>
+        <v>105.29</v>
       </c>
       <c r="AB26" t="n">
-        <v>199.59</v>
+        <v>113.77</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>THOMAS COOK (INDIA) LIMITED</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3045,96 +3045,96 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>105.71</v>
+        <v>508.8</v>
       </c>
       <c r="J27" t="n">
-        <v>109.31</v>
+        <v>545.03</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.3</v>
+        <v>-6.6</v>
       </c>
       <c r="L27" t="n">
-        <v>72.34</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>48.4</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.971</v>
+        <v>0.034</v>
       </c>
       <c r="Q27" t="n">
-        <v>4985</v>
+        <v>3199</v>
       </c>
       <c r="R27" t="n">
-        <v>40</v>
+        <v>21.7</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T27" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="U27" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="V27" t="n">
-        <v>1.25</v>
+        <v>3.73</v>
       </c>
       <c r="W27" t="n">
-        <v>9.710000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="X27" t="n">
-        <v>0.06</v>
+        <v>0.62</v>
       </c>
       <c r="Y27" t="b">
         <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AA27" t="n">
-        <v>105.29</v>
+        <v>528.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>113.77</v>
+        <v>562.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>BAJAJHCARE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>BAJAJ HEALTHCARE LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3142,10 +3142,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F28" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G28" t="n">
         <v>5</v>
@@ -3154,80 +3154,80 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>508.8</v>
+        <v>329</v>
       </c>
       <c r="J28" t="n">
-        <v>545.03</v>
+        <v>297.3</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.6</v>
+        <v>10.7</v>
       </c>
       <c r="L28" t="n">
-        <v>69.90000000000001</v>
+        <v>67.69</v>
       </c>
       <c r="M28" t="n">
-        <v>1.09</v>
+        <v>2.97</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.034</v>
+        <v>0.27</v>
       </c>
       <c r="Q28" t="n">
-        <v>3207</v>
+        <v>1098</v>
       </c>
       <c r="R28" t="n">
-        <v>21.7</v>
+        <v>19.5</v>
       </c>
       <c r="S28" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T28" t="n">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="U28" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="V28" t="n">
-        <v>3.73</v>
+        <v>4.07</v>
       </c>
       <c r="W28" t="n">
-        <v>19.8</v>
+        <v>11.5</v>
       </c>
       <c r="X28" t="n">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="Y28" t="b">
         <v>1</v>
       </c>
       <c r="Z28" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="AA28" t="n">
-        <v>528.83</v>
+        <v>334.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>562.2</v>
+        <v>348.71</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.7</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BAJAJ HEALTHCARE LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3239,96 +3239,96 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>207.76</v>
+      </c>
+      <c r="J29" t="n">
+        <v>210.35</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>67.04000000000001</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N29" t="n">
         <v>5</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>329</v>
-      </c>
-      <c r="J29" t="n">
-        <v>297.3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="L29" t="n">
-        <v>67.69</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.268</v>
+        <v>0.149</v>
       </c>
       <c r="Q29" t="n">
-        <v>1108</v>
+        <v>194</v>
       </c>
       <c r="R29" t="n">
-        <v>19.7</v>
+        <v>24.1</v>
       </c>
       <c r="S29" t="n">
         <v>12</v>
       </c>
       <c r="T29" t="n">
-        <v>29</v>
+        <v>0.03</v>
       </c>
       <c r="U29" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V29" t="n">
-        <v>4.07</v>
+        <v>0.03</v>
       </c>
       <c r="W29" t="n">
-        <v>11.5</v>
+        <v>7.91</v>
       </c>
       <c r="X29" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>17</v>
+        <v>3.16</v>
       </c>
       <c r="AA29" t="n">
-        <v>334.4</v>
+        <v>207.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>348.71</v>
+        <v>194.97</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.1</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3336,96 +3336,96 @@
         </is>
       </c>
       <c r="E30" t="n">
+        <v>17</v>
+      </c>
+      <c r="F30" t="n">
+        <v>30</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>171.12</v>
+      </c>
+      <c r="J30" t="n">
+        <v>175.74</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>74.59</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2160</v>
+      </c>
+      <c r="R30" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="S30" t="n">
         <v>20</v>
       </c>
-      <c r="F30" t="n">
-        <v>10</v>
-      </c>
-      <c r="G30" t="n">
-        <v>20</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I30" t="n">
-        <v>207.76</v>
-      </c>
-      <c r="J30" t="n">
-        <v>210.35</v>
-      </c>
-      <c r="K30" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="L30" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="N30" t="n">
-        <v>5</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>27-08-2026</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>197</v>
-      </c>
-      <c r="R30" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>12</v>
-      </c>
       <c r="T30" t="n">
-        <v>0.03</v>
+        <v>17</v>
       </c>
       <c r="U30" t="n">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="V30" t="n">
-        <v>0.03</v>
+        <v>0.8</v>
       </c>
       <c r="W30" t="n">
-        <v>7.91</v>
+        <v>30.3</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.16</v>
+        <v>23</v>
       </c>
       <c r="AA30" t="n">
-        <v>207.03</v>
+        <v>191.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>194.97</v>
+        <v>550.58</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.1</v>
+        <v>-88.09999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3433,96 +3433,92 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F31" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="I31" t="n">
-        <v>171.12</v>
+        <v>13.34</v>
       </c>
       <c r="J31" t="n">
-        <v>175.74</v>
+        <v>12.41</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.6</v>
+        <v>7.5</v>
       </c>
       <c r="L31" t="n">
-        <v>74.59</v>
+        <v>69.12</v>
       </c>
       <c r="M31" t="n">
-        <v>0.49</v>
+        <v>1.48</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.023</v>
+        <v>0.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>2168</v>
+        <v>370</v>
       </c>
       <c r="R31" t="n">
-        <v>49.8</v>
+        <v>1192</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
-      </c>
-      <c r="T31" t="n">
-        <v>17</v>
-      </c>
+        <v>-61</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="n">
-        <v>83</v>
+        <v>-98</v>
       </c>
       <c r="V31" t="n">
-        <v>0.8</v>
+        <v>0.01</v>
       </c>
       <c r="W31" t="n">
-        <v>30.3</v>
+        <v>2.46</v>
       </c>
       <c r="X31" t="n">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="Y31" t="b">
         <v>1</v>
       </c>
-      <c r="Z31" t="n">
-        <v>23</v>
-      </c>
+      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="n">
-        <v>191.63</v>
+        <v>11.16</v>
       </c>
       <c r="AB31" t="n">
-        <v>550.58</v>
+        <v>13.51</v>
       </c>
       <c r="AC31" t="n">
-        <v>-88.09999999999999</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>EUROPRATIK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>Euro Pratik Sales Limited</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3530,92 +3526,96 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G32" t="n">
         <v>15</v>
       </c>
       <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>259.35</v>
+      </c>
+      <c r="J32" t="n">
+        <v>257.65</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>29-05-2026</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2695</v>
+      </c>
+      <c r="R32" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="S32" t="n">
         <v>-3</v>
       </c>
-      <c r="I32" t="n">
-        <v>13.34</v>
-      </c>
-      <c r="J32" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="K32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L32" t="n">
-        <v>69.12</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="N32" t="n">
-        <v>13</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>379</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1221</v>
-      </c>
-      <c r="S32" t="n">
-        <v>-61</v>
-      </c>
-      <c r="T32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>11</v>
+      </c>
       <c r="U32" t="n">
-        <v>-98</v>
+        <v>3</v>
       </c>
       <c r="V32" t="n">
-        <v>0.01</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>2.46</v>
+        <v>29.6</v>
       </c>
       <c r="X32" t="n">
-        <v>0.44</v>
+        <v>0.03</v>
       </c>
       <c r="Y32" t="b">
         <v>1</v>
       </c>
-      <c r="Z32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>24</v>
+      </c>
       <c r="AA32" t="n">
-        <v>11.16</v>
+        <v>293.68</v>
       </c>
       <c r="AB32" t="n">
-        <v>13.51</v>
+        <v>277.19</v>
       </c>
       <c r="AC32" t="n">
-        <v>-11.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EUROPRATIK</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Euro Pratik Sales Limited</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3623,81 +3623,79 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>259.35</v>
+        <v>739.5</v>
       </c>
       <c r="J33" t="n">
-        <v>257.65</v>
+        <v>717.77</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>70.09</v>
+        <v>61.71</v>
       </c>
       <c r="M33" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.062</v>
+        <v>0.722</v>
       </c>
       <c r="Q33" t="n">
-        <v>2649</v>
-      </c>
-      <c r="R33" t="n">
-        <v>46.1</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>-3</v>
+        <v>9</v>
       </c>
       <c r="T33" t="n">
-        <v>11</v>
+        <v>11.91</v>
       </c>
       <c r="U33" t="n">
-        <v>3</v>
+        <v>-184</v>
       </c>
       <c r="V33" t="n">
-        <v>1.05</v>
+        <v>31.98</v>
       </c>
       <c r="W33" t="n">
-        <v>29.6</v>
+        <v>0.27</v>
       </c>
       <c r="X33" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="Y33" t="b">
         <v>1</v>
       </c>
       <c r="Z33" t="n">
-        <v>24</v>
+        <v>57.93</v>
       </c>
       <c r="AA33" t="n">
-        <v>293.68</v>
+        <v>730.45</v>
       </c>
       <c r="AB33" t="n">
-        <v>277.19</v>
+        <v>761.02</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3753,10 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.716</v>
+        <v>1.73</v>
       </c>
       <c r="Q34" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
@@ -3798,16 +3796,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>AJMERA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>AJMERA REALTY &amp; INFRA INDIA LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3815,90 +3813,92 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F35" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>739.5</v>
+        <v>115.67</v>
       </c>
       <c r="J35" t="n">
-        <v>717.77</v>
+        <v>114.86</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="L35" t="n">
-        <v>61.71</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>1.61</v>
+        <v>7.36</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.703</v>
+        <v>0.328</v>
       </c>
       <c r="Q35" t="n">
-        <v>229</v>
-      </c>
-      <c r="R35" t="inlineStr"/>
+        <v>2244</v>
+      </c>
+      <c r="R35" t="n">
+        <v>19.3</v>
+      </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T35" t="n">
-        <v>11.91</v>
+        <v>46</v>
       </c>
       <c r="U35" t="n">
-        <v>-184</v>
+        <v>-4</v>
       </c>
       <c r="V35" t="n">
-        <v>31.98</v>
+        <v>1.17</v>
       </c>
       <c r="W35" t="n">
-        <v>0.27</v>
+        <v>14.2</v>
       </c>
       <c r="X35" t="n">
-        <v>0.1</v>
+        <v>0.46</v>
       </c>
       <c r="Y35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>57.93</v>
+        <v>38</v>
       </c>
       <c r="AA35" t="n">
-        <v>730.45</v>
+        <v>125.35</v>
       </c>
       <c r="AB35" t="n">
-        <v>761.02</v>
+        <v>318.92</v>
       </c>
       <c r="AC35" t="n">
-        <v>-5.6</v>
+        <v>-12.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AJMERA</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AJMERA REALTY &amp; INFRA INDIA LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3913,78 +3913,78 @@
         <v>25</v>
       </c>
       <c r="F36" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H36" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="J36" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N36" t="n">
+        <v>22</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>26-08-2026</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>407</v>
+      </c>
+      <c r="R36" t="n">
+        <v>101</v>
+      </c>
+      <c r="S36" t="n">
+        <v>246</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="U36" t="n">
+        <v>10</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X36" t="n">
         <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>115.67</v>
-      </c>
-      <c r="J36" t="n">
-        <v>114.86</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L36" t="n">
-        <v>69.73999999999999</v>
-      </c>
-      <c r="M36" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="N36" t="n">
-        <v>4</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>04-06-2026</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2279</v>
-      </c>
-      <c r="R36" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="S36" t="n">
-        <v>18</v>
-      </c>
-      <c r="T36" t="n">
-        <v>46</v>
-      </c>
-      <c r="U36" t="n">
-        <v>-4</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W36" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0.46</v>
       </c>
       <c r="Y36" t="b">
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>38</v>
+        <v>4.21</v>
       </c>
       <c r="AA36" t="n">
-        <v>125.35</v>
+        <v>40.71</v>
       </c>
       <c r="AB36" t="n">
-        <v>318.92</v>
+        <v>39.67</v>
       </c>
       <c r="AC36" t="n">
-        <v>-12.2</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="37">
@@ -4042,13 +4042,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="Q37" t="n">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="R37" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="S37" t="n">
         <v>185</v>
@@ -4137,13 +4137,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.277</v>
+        <v>0.281</v>
       </c>
       <c r="Q38" t="n">
-        <v>3684</v>
+        <v>3632</v>
       </c>
       <c r="R38" t="n">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4182,12 +4182,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4199,90 +4199,92 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F39" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I39" t="n">
-        <v>169.08</v>
+        <v>111.83</v>
       </c>
       <c r="J39" t="n">
-        <v>182.69</v>
+        <v>113.42</v>
       </c>
       <c r="K39" t="n">
-        <v>-7.4</v>
+        <v>-1.4</v>
       </c>
       <c r="L39" t="n">
-        <v>69.05</v>
+        <v>73.48</v>
       </c>
       <c r="M39" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.128</v>
+        <v>0.304</v>
       </c>
       <c r="Q39" t="n">
-        <v>580</v>
+        <v>214</v>
       </c>
       <c r="R39" t="n">
-        <v>13.7</v>
+        <v>25.5</v>
       </c>
       <c r="S39" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="T39" t="n">
-        <v>15</v>
+        <v>12.07</v>
       </c>
       <c r="U39" t="n">
-        <v>82</v>
+        <v>-29</v>
       </c>
       <c r="V39" t="n">
-        <v>3.07</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>42.7</v>
+        <v>7.92</v>
       </c>
       <c r="X39" t="n">
-        <v>0.35</v>
+        <v>0.98</v>
       </c>
       <c r="Y39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="n">
-        <v>12</v>
+        <v>4.11</v>
       </c>
       <c r="AA39" t="n">
-        <v>171.39</v>
-      </c>
-      <c r="AB39" t="inlineStr"/>
+        <v>111.31</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>119.92</v>
+      </c>
       <c r="AC39" t="n">
-        <v>-12.6</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4294,92 +4296,90 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>111.83</v>
+        <v>169.08</v>
       </c>
       <c r="J40" t="n">
-        <v>113.5</v>
+        <v>182.69</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.5</v>
+        <v>-7.4</v>
       </c>
       <c r="L40" t="n">
-        <v>73.48</v>
+        <v>69.05</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="N40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.282</v>
+        <v>0.128</v>
       </c>
       <c r="Q40" t="n">
-        <v>213</v>
+        <v>577</v>
       </c>
       <c r="R40" t="n">
-        <v>25.4</v>
+        <v>13.6</v>
       </c>
       <c r="S40" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="T40" t="n">
-        <v>12.07</v>
+        <v>15</v>
       </c>
       <c r="U40" t="n">
-        <v>-29</v>
+        <v>82</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>3.07</v>
       </c>
       <c r="W40" t="n">
-        <v>7.92</v>
+        <v>42.7</v>
       </c>
       <c r="X40" t="n">
-        <v>0.98</v>
+        <v>0.35</v>
       </c>
       <c r="Y40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.11</v>
+        <v>12</v>
       </c>
       <c r="AA40" t="n">
-        <v>111.31</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>119.92</v>
-      </c>
+        <v>171.39</v>
+      </c>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>-3.1</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -4394,89 +4394,89 @@
         <v>17</v>
       </c>
       <c r="F41" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>55.28</v>
+        <v>266.6</v>
       </c>
       <c r="J41" t="n">
-        <v>60.15</v>
+        <v>269.7</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.1</v>
+        <v>-1.1</v>
       </c>
       <c r="L41" t="n">
-        <v>73.01000000000001</v>
+        <v>73.09</v>
       </c>
       <c r="M41" t="n">
-        <v>0.9</v>
+        <v>1.48</v>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.188</v>
+        <v>0.099</v>
       </c>
       <c r="Q41" t="n">
-        <v>480</v>
+        <v>1500</v>
       </c>
       <c r="R41" t="n">
-        <v>12</v>
+        <v>13.6</v>
       </c>
       <c r="S41" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="T41" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="U41" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V41" t="n">
-        <v>1.22</v>
+        <v>4.31</v>
       </c>
       <c r="W41" t="n">
-        <v>12</v>
+        <v>13.6</v>
       </c>
       <c r="X41" t="n">
-        <v>0.58</v>
+        <v>0.28</v>
       </c>
       <c r="Y41" t="b">
         <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.4</v>
+        <v>12</v>
       </c>
       <c r="AA41" t="n">
-        <v>57.78</v>
+        <v>268.2</v>
       </c>
       <c r="AB41" t="n">
-        <v>59.21</v>
+        <v>293.62</v>
       </c>
       <c r="AC41" t="n">
-        <v>-8.4</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4491,93 +4491,93 @@
         <v>17</v>
       </c>
       <c r="F42" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I42" t="n">
-        <v>266.6</v>
+        <v>55.28</v>
       </c>
       <c r="J42" t="n">
-        <v>269.7</v>
+        <v>60.15</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.1</v>
+        <v>-8.1</v>
       </c>
       <c r="L42" t="n">
-        <v>73.09</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.098</v>
+        <v>0.188</v>
       </c>
       <c r="Q42" t="n">
-        <v>1510</v>
+        <v>479</v>
       </c>
       <c r="R42" t="n">
-        <v>13.6</v>
+        <v>12</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="T42" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="U42" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V42" t="n">
-        <v>4.31</v>
+        <v>1.22</v>
       </c>
       <c r="W42" t="n">
-        <v>13.6</v>
+        <v>12</v>
       </c>
       <c r="X42" t="n">
-        <v>0.28</v>
+        <v>0.58</v>
       </c>
       <c r="Y42" t="b">
         <v>1</v>
       </c>
       <c r="Z42" t="n">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="AA42" t="n">
-        <v>268.2</v>
+        <v>57.78</v>
       </c>
       <c r="AB42" t="n">
-        <v>293.62</v>
+        <v>59.21</v>
       </c>
       <c r="AC42" t="n">
-        <v>-7.5</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>GRMOVER</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>GRM OVERSEAS LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4585,96 +4585,96 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F43" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>85.29000000000001</v>
+      </c>
+      <c r="J43" t="n">
+        <v>95.54000000000001</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="L43" t="n">
+        <v>71.72</v>
+      </c>
+      <c r="M43" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="N43" t="n">
+        <v>6</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1756</v>
+      </c>
+      <c r="R43" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="S43" t="n">
+        <v>39</v>
+      </c>
+      <c r="T43" t="n">
+        <v>31</v>
+      </c>
+      <c r="U43" t="n">
         <v>8</v>
       </c>
-      <c r="G43" t="n">
-        <v>15</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I43" t="n">
-        <v>41.53</v>
-      </c>
-      <c r="J43" t="n">
-        <v>43.04</v>
-      </c>
-      <c r="K43" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="L43" t="n">
-        <v>71.79000000000001</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N43" t="n">
-        <v>22</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
-      <c r="P43" t="n">
-        <v>0.248</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>412</v>
-      </c>
-      <c r="R43" t="n">
-        <v>102</v>
-      </c>
-      <c r="S43" t="n">
-        <v>246</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="U43" t="n">
-        <v>10</v>
-      </c>
       <c r="V43" t="n">
-        <v>0.14</v>
+        <v>0.9</v>
       </c>
       <c r="W43" t="n">
-        <v>2.16</v>
+        <v>11.3</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y43" t="b">
         <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.21</v>
+        <v>9</v>
       </c>
       <c r="AA43" t="n">
-        <v>40.71</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="AB43" t="n">
-        <v>39.67</v>
+        <v>188.11</v>
       </c>
       <c r="AC43" t="n">
-        <v>-0.2</v>
+        <v>-48.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GRM OVERSEAS LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4682,10 +4682,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -4694,84 +4694,84 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>85.29000000000001</v>
+        <v>173.3</v>
       </c>
       <c r="J44" t="n">
-        <v>95.54000000000001</v>
+        <v>173.91</v>
       </c>
       <c r="K44" t="n">
-        <v>-10.7</v>
+        <v>-0.4</v>
       </c>
       <c r="L44" t="n">
-        <v>71.72</v>
+        <v>65.64</v>
       </c>
       <c r="M44" t="n">
-        <v>10.87</v>
+        <v>2.61</v>
       </c>
       <c r="N44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.615</v>
+        <v>0.138</v>
       </c>
       <c r="Q44" t="n">
-        <v>1768</v>
+        <v>1891</v>
       </c>
       <c r="R44" t="n">
-        <v>31.9</v>
+        <v>20</v>
       </c>
       <c r="S44" t="n">
-        <v>39</v>
+        <v>-3</v>
       </c>
       <c r="T44" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="U44" t="n">
-        <v>8</v>
+        <v>-4</v>
       </c>
       <c r="V44" t="n">
-        <v>0.9</v>
+        <v>2.36</v>
       </c>
       <c r="W44" t="n">
-        <v>11.3</v>
+        <v>14.2</v>
       </c>
       <c r="X44" t="n">
-        <v>0.67</v>
+        <v>0.01</v>
       </c>
       <c r="Y44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="AA44" t="n">
-        <v>91.23999999999999</v>
+        <v>183.62</v>
       </c>
       <c r="AB44" t="n">
-        <v>188.11</v>
+        <v>190.35</v>
       </c>
       <c r="AC44" t="n">
-        <v>-48.1</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>MBEL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>M &amp; B Engineering Limited</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4791,84 +4791,84 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>173.3</v>
+        <v>265.6</v>
       </c>
       <c r="J45" t="n">
-        <v>173.91</v>
+        <v>292.28</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.4</v>
+        <v>-9.1</v>
       </c>
       <c r="L45" t="n">
-        <v>65.64</v>
+        <v>70.45</v>
       </c>
       <c r="M45" t="n">
-        <v>2.61</v>
+        <v>1.29</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.136</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q45" t="n">
-        <v>1924</v>
+        <v>1507</v>
       </c>
       <c r="R45" t="n">
-        <v>20.4</v>
+        <v>19.1</v>
       </c>
       <c r="S45" t="n">
-        <v>-3</v>
+        <v>13</v>
       </c>
       <c r="T45" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="U45" t="n">
         <v>-4</v>
       </c>
       <c r="V45" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="W45" t="n">
-        <v>14.2</v>
+        <v>19.9</v>
       </c>
       <c r="X45" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="Y45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="AA45" t="n">
-        <v>183.62</v>
+        <v>297.01</v>
       </c>
       <c r="AB45" t="n">
-        <v>190.35</v>
+        <v>322.67</v>
       </c>
       <c r="AC45" t="n">
-        <v>-14.5</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MBEL</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>M &amp; B Engineering Limited</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4885,184 +4885,174 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I46" t="n">
-        <v>265.6</v>
+        <v>28.15</v>
       </c>
       <c r="J46" t="n">
-        <v>292.28</v>
+        <v>34.54</v>
       </c>
       <c r="K46" t="n">
-        <v>-9.1</v>
+        <v>-18.5</v>
       </c>
       <c r="L46" t="n">
-        <v>70.45</v>
+        <v>61.81</v>
       </c>
       <c r="M46" t="n">
-        <v>1.29</v>
+        <v>0.88</v>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.295</v>
       </c>
       <c r="Q46" t="n">
-        <v>1512</v>
+        <v>298</v>
       </c>
       <c r="R46" t="n">
-        <v>19.2</v>
+        <v>15.7</v>
       </c>
       <c r="S46" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T46" t="n">
-        <v>21</v>
+        <v>2.79</v>
       </c>
       <c r="U46" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
       <c r="V46" t="n">
-        <v>2.56</v>
+        <v>0.21</v>
       </c>
       <c r="W46" t="n">
-        <v>19.9</v>
+        <v>17.6</v>
       </c>
       <c r="X46" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="Y46" t="b">
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>8</v>
+        <v>1.83</v>
       </c>
       <c r="AA46" t="n">
-        <v>297.01</v>
+        <v>30.89</v>
       </c>
       <c r="AB46" t="n">
-        <v>322.67</v>
+        <v>33.18</v>
       </c>
       <c r="AC46" t="n">
-        <v>-12.3</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F47" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G47" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" t="n">
         <v>0</v>
       </c>
-      <c r="H47" t="n">
-        <v>-2</v>
-      </c>
       <c r="I47" t="n">
-        <v>28.15</v>
+        <v>66.19</v>
       </c>
       <c r="J47" t="n">
-        <v>34.54</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-18.5</v>
+        <v>3.4</v>
       </c>
       <c r="L47" t="n">
-        <v>61.81</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>0.88</v>
+        <v>0.31</v>
       </c>
       <c r="N47" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.294</v>
+        <v>0.038</v>
       </c>
       <c r="Q47" t="n">
-        <v>299</v>
+        <v>811</v>
       </c>
       <c r="R47" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="S47" t="n">
-        <v>16</v>
-      </c>
+        <v>19.4</v>
+      </c>
+      <c r="S47" t="inlineStr"/>
       <c r="T47" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U47" t="n">
-        <v>-30</v>
-      </c>
+        <v>12.31</v>
+      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="W47" t="n">
-        <v>17.6</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="W47" t="inlineStr"/>
       <c r="X47" t="n">
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
       <c r="Y47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.83</v>
+        <v>12.14</v>
       </c>
       <c r="AA47" t="n">
-        <v>30.89</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>33.18</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>-12.1</v>
-      </c>
+        <v>66.77</v>
+      </c>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5070,167 +5060,80 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F48" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I48" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="J48" t="n">
+        <v>100.33</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="L48" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>857</v>
+      </c>
+      <c r="R48" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="S48" t="n">
         <v>9</v>
       </c>
-      <c r="G48" t="n">
-        <v>5</v>
-      </c>
-      <c r="H48" t="n">
+      <c r="T48" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="U48" t="n">
+        <v>-36</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="W48" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Y48" t="b">
         <v>0</v>
       </c>
-      <c r="I48" t="n">
-        <v>66.19</v>
-      </c>
-      <c r="J48" t="n">
-        <v>64.04000000000001</v>
-      </c>
-      <c r="K48" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L48" t="n">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N48" t="n">
-        <v>3</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>807</v>
-      </c>
-      <c r="R48" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="n">
-        <v>12.31</v>
-      </c>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Y48" t="b">
-        <v>1</v>
-      </c>
       <c r="Z48" t="n">
-        <v>12.14</v>
+        <v>4.02</v>
       </c>
       <c r="AA48" t="n">
-        <v>66.77</v>
-      </c>
-      <c r="AB48" t="inlineStr"/>
-      <c r="AC48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>WCIL</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>26</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>20</v>
-      </c>
-      <c r="F49" t="n">
-        <v>8</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I49" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="J49" t="n">
-        <v>100.33</v>
-      </c>
-      <c r="K49" t="n">
-        <v>-15.4</v>
-      </c>
-      <c r="L49" t="n">
-        <v>71.89</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="N49" t="n">
-        <v>5</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>30-06-2026</t>
-        </is>
-      </c>
-      <c r="P49" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>865</v>
-      </c>
-      <c r="R49" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="S49" t="n">
-        <v>9</v>
-      </c>
-      <c r="T49" t="n">
-        <v>18.68</v>
-      </c>
-      <c r="U49" t="n">
-        <v>-36</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="W49" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="Y49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="AA49" t="n">
         <v>91.7</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AB48" t="n">
         <v>103.94</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AC48" t="n">
         <v>-25.9</v>
       </c>
     </row>
@@ -5245,7 +5148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5379,175 +5282,175 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MACPOWER CNC MACHINES LIMITED</t>
+          <t>Alembic Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1911.3</v>
+        <v>843.85</v>
       </c>
       <c r="D4" t="n">
-        <v>920.51</v>
+        <v>746.02</v>
       </c>
       <c r="E4" t="n">
-        <v>107.6</v>
+        <v>13.1</v>
       </c>
       <c r="F4" t="n">
-        <v>73.16</v>
+        <v>69.61</v>
       </c>
       <c r="G4" t="n">
-        <v>0.44</v>
+        <v>7.69</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Limited</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>843.85</v>
+        <v>263.2</v>
       </c>
       <c r="D5" t="n">
-        <v>745.6900000000001</v>
+        <v>217.8</v>
       </c>
       <c r="E5" t="n">
-        <v>13.2</v>
+        <v>20.8</v>
       </c>
       <c r="F5" t="n">
-        <v>69.61</v>
+        <v>71.75</v>
       </c>
       <c r="G5" t="n">
-        <v>9.18</v>
+        <v>0.82</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>THANGAMAIYL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>263.2</v>
+        <v>5311.5</v>
       </c>
       <c r="D6" t="n">
-        <v>217.8</v>
+        <v>5198.76</v>
       </c>
       <c r="E6" t="n">
-        <v>20.8</v>
+        <v>2.2</v>
       </c>
       <c r="F6" t="n">
-        <v>71.75</v>
+        <v>67.16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.82</v>
+        <v>7.21</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>THANGAMAIYL JEWELLERY LIMITED</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5311.5</v>
+        <v>70.09</v>
       </c>
       <c r="D7" t="n">
-        <v>5198.76</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2</v>
+        <v>-0.4</v>
       </c>
       <c r="F7" t="n">
-        <v>67.16</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>7.21</v>
+        <v>1.04</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>70.09</v>
+        <v>511.25</v>
       </c>
       <c r="D8" t="n">
-        <v>70.34999999999999</v>
+        <v>390.61</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4</v>
+        <v>30.9</v>
       </c>
       <c r="F8" t="n">
-        <v>72.56999999999999</v>
+        <v>63.09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.04</v>
+        <v>8.02</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
@@ -5589,35 +5492,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>511.25</v>
+        <v>190.05</v>
       </c>
       <c r="D10" t="n">
-        <v>390.61</v>
+        <v>164.1</v>
       </c>
       <c r="E10" t="n">
-        <v>30.9</v>
+        <v>15.8</v>
       </c>
       <c r="F10" t="n">
-        <v>63.09</v>
+        <v>60.6</v>
       </c>
       <c r="G10" t="n">
-        <v>8.02</v>
+        <v>0.25</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
@@ -5694,735 +5597,735 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>190.05</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>164.1</v>
+        <v>91.62</v>
       </c>
       <c r="E13" t="n">
-        <v>15.8</v>
+        <v>7.9</v>
       </c>
       <c r="F13" t="n">
-        <v>60.6</v>
+        <v>70.88</v>
       </c>
       <c r="G13" t="n">
-        <v>0.25</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>98.84999999999999</v>
+        <v>623.1</v>
       </c>
       <c r="D14" t="n">
-        <v>91.62</v>
+        <v>577.97</v>
       </c>
       <c r="E14" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="F14" t="n">
-        <v>70.88</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>8.390000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>623.1</v>
+        <v>339</v>
       </c>
       <c r="D15" t="n">
-        <v>577.97</v>
+        <v>314.32</v>
       </c>
       <c r="E15" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="F15" t="n">
-        <v>64.68000000000001</v>
+        <v>63.24</v>
       </c>
       <c r="G15" t="n">
-        <v>5.8</v>
+        <v>1.74</v>
       </c>
       <c r="H15" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>NUPUR RECYCLERS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>339</v>
+        <v>120.05</v>
       </c>
       <c r="D16" t="n">
-        <v>314.32</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>7.9</v>
+        <v>44.8</v>
       </c>
       <c r="F16" t="n">
-        <v>63.24</v>
+        <v>72.53</v>
       </c>
       <c r="G16" t="n">
-        <v>1.74</v>
+        <v>0.42</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NUPUR RECYCLERS LIMITED</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>120.05</v>
+        <v>19.84</v>
       </c>
       <c r="D17" t="n">
-        <v>82.93000000000001</v>
+        <v>21.01</v>
       </c>
       <c r="E17" t="n">
-        <v>44.8</v>
+        <v>-5.6</v>
       </c>
       <c r="F17" t="n">
-        <v>72.53</v>
+        <v>70.87</v>
       </c>
       <c r="G17" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
         <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19.84</v>
+        <v>82.91</v>
       </c>
       <c r="D18" t="n">
-        <v>21.01</v>
+        <v>76.98</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.6</v>
+        <v>7.7</v>
       </c>
       <c r="F18" t="n">
-        <v>70.87</v>
+        <v>62.78</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>2.64</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>RGL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>Renaissance Global Limited</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>82.91</v>
+        <v>136.96</v>
       </c>
       <c r="D19" t="n">
-        <v>76.98</v>
+        <v>100.9</v>
       </c>
       <c r="E19" t="n">
-        <v>7.7</v>
+        <v>35.7</v>
       </c>
       <c r="F19" t="n">
-        <v>62.78</v>
+        <v>69.56</v>
       </c>
       <c r="G19" t="n">
-        <v>2.64</v>
+        <v>3.01</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RGL</t>
+          <t>DIAMONDYD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Renaissance Global Limited</t>
+          <t>Prataap Snacks Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>136.96</v>
+        <v>1144.8</v>
       </c>
       <c r="D20" t="n">
-        <v>100.9</v>
+        <v>1174.34</v>
       </c>
       <c r="E20" t="n">
-        <v>35.7</v>
+        <v>-2.5</v>
       </c>
       <c r="F20" t="n">
-        <v>69.56</v>
+        <v>69.75</v>
       </c>
       <c r="G20" t="n">
-        <v>3.01</v>
+        <v>65.58</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DIAMONDYD</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Prataap Snacks Limited</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1144.8</v>
+        <v>494.45</v>
       </c>
       <c r="D21" t="n">
-        <v>1174.34</v>
+        <v>479.69</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5</v>
+        <v>3.1</v>
       </c>
       <c r="F21" t="n">
-        <v>69.75</v>
+        <v>62.09</v>
       </c>
       <c r="G21" t="n">
-        <v>65.58</v>
+        <v>0.66</v>
       </c>
       <c r="H21" t="n">
         <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>494.45</v>
+        <v>28.03</v>
       </c>
       <c r="D22" t="n">
-        <v>479.69</v>
+        <v>29.14</v>
       </c>
       <c r="E22" t="n">
-        <v>3.1</v>
+        <v>-3.8</v>
       </c>
       <c r="F22" t="n">
-        <v>62.09</v>
+        <v>69.03</v>
       </c>
       <c r="G22" t="n">
-        <v>0.66</v>
+        <v>1.34</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.03</v>
+        <v>1351.4</v>
       </c>
       <c r="D23" t="n">
-        <v>29.14</v>
+        <v>1104.34</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8</v>
+        <v>22.4</v>
       </c>
       <c r="F23" t="n">
-        <v>69.03</v>
+        <v>60.82</v>
       </c>
       <c r="G23" t="n">
-        <v>1.34</v>
+        <v>5.22</v>
       </c>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1351.4</v>
+        <v>124.56</v>
       </c>
       <c r="D24" t="n">
-        <v>1104.34</v>
+        <v>105.19</v>
       </c>
       <c r="E24" t="n">
-        <v>22.4</v>
+        <v>18.4</v>
       </c>
       <c r="F24" t="n">
-        <v>60.82</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>5.22</v>
+        <v>2.63</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>124.56</v>
+        <v>168.2</v>
       </c>
       <c r="D25" t="n">
-        <v>105.19</v>
+        <v>201.21</v>
       </c>
       <c r="E25" t="n">
-        <v>18.4</v>
+        <v>-16.4</v>
       </c>
       <c r="F25" t="n">
-        <v>67.15000000000001</v>
+        <v>64.08</v>
       </c>
       <c r="G25" t="n">
-        <v>2.63</v>
+        <v>8.07</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>THOMAS COOK (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>168.2</v>
+        <v>105.71</v>
       </c>
       <c r="D26" t="n">
-        <v>201.21</v>
+        <v>109.31</v>
       </c>
       <c r="E26" t="n">
-        <v>-16.4</v>
+        <v>-3.3</v>
       </c>
       <c r="F26" t="n">
-        <v>64.08</v>
+        <v>72.34</v>
       </c>
       <c r="G26" t="n">
-        <v>8.07</v>
+        <v>48.4</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>THOMAS COOK (INDIA) LIMITED</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>105.71</v>
+        <v>508.8</v>
       </c>
       <c r="D27" t="n">
-        <v>109.31</v>
+        <v>545.03</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.3</v>
+        <v>-6.6</v>
       </c>
       <c r="F27" t="n">
-        <v>72.34</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>48.4</v>
+        <v>1.09</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>BAJAJHCARE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>BAJAJ HEALTHCARE LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>508.8</v>
+        <v>329</v>
       </c>
       <c r="D28" t="n">
-        <v>545.03</v>
+        <v>297.3</v>
       </c>
       <c r="E28" t="n">
-        <v>-6.6</v>
+        <v>10.7</v>
       </c>
       <c r="F28" t="n">
-        <v>69.90000000000001</v>
+        <v>67.69</v>
       </c>
       <c r="G28" t="n">
-        <v>1.09</v>
+        <v>2.97</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BAJAJ HEALTHCARE LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>329</v>
+        <v>207.76</v>
       </c>
       <c r="D29" t="n">
-        <v>297.3</v>
+        <v>210.35</v>
       </c>
       <c r="E29" t="n">
-        <v>10.7</v>
+        <v>-1.2</v>
       </c>
       <c r="F29" t="n">
-        <v>67.69</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>2.97</v>
+        <v>0.29</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>207.76</v>
+        <v>171.12</v>
       </c>
       <c r="D30" t="n">
-        <v>210.35</v>
+        <v>175.74</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.2</v>
+        <v>-2.6</v>
       </c>
       <c r="F30" t="n">
-        <v>67.04000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="G30" t="n">
-        <v>0.29</v>
+        <v>0.49</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>171.12</v>
+        <v>13.34</v>
       </c>
       <c r="D31" t="n">
-        <v>175.74</v>
+        <v>12.41</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.6</v>
+        <v>7.5</v>
       </c>
       <c r="F31" t="n">
-        <v>74.59</v>
+        <v>69.12</v>
       </c>
       <c r="G31" t="n">
-        <v>0.49</v>
+        <v>1.48</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>EUROPRATIK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>Euro Pratik Sales Limited</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13.34</v>
+        <v>259.35</v>
       </c>
       <c r="D32" t="n">
-        <v>12.4</v>
+        <v>257.65</v>
       </c>
       <c r="E32" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="F32" t="n">
-        <v>69.12</v>
+        <v>70.09</v>
       </c>
       <c r="G32" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="H32" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>29-05-2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EUROPRATIK</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Euro Pratik Sales Limited</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>259.35</v>
+        <v>739.5</v>
       </c>
       <c r="D33" t="n">
-        <v>257.65</v>
+        <v>717.77</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>70.09</v>
+        <v>61.71</v>
       </c>
       <c r="G33" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
     </row>
@@ -6464,70 +6367,70 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>AJMERA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>AJMERA REALTY &amp; INFRA INDIA LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>739.5</v>
+        <v>115.67</v>
       </c>
       <c r="D35" t="n">
-        <v>717.77</v>
+        <v>114.86</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="F35" t="n">
-        <v>61.71</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>1.61</v>
+        <v>7.36</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AJMERA</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AJMERA REALTY &amp; INFRA INDIA LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>115.67</v>
+        <v>41.53</v>
       </c>
       <c r="D36" t="n">
-        <v>114.86</v>
+        <v>43.04</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7</v>
+        <v>-3.5</v>
       </c>
       <c r="F36" t="n">
-        <v>69.73999999999999</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36</v>
+        <v>1.02</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
     </row>
@@ -6604,383 +6507,348 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>169.08</v>
+        <v>111.83</v>
       </c>
       <c r="D39" t="n">
-        <v>182.69</v>
+        <v>113.42</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.4</v>
+        <v>-1.4</v>
       </c>
       <c r="F39" t="n">
-        <v>69.05</v>
+        <v>73.48</v>
       </c>
       <c r="G39" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>111.83</v>
+        <v>169.08</v>
       </c>
       <c r="D40" t="n">
-        <v>113.5</v>
+        <v>182.69</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5</v>
+        <v>-7.4</v>
       </c>
       <c r="F40" t="n">
-        <v>73.48</v>
+        <v>69.05</v>
       </c>
       <c r="G40" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>55.28</v>
+        <v>266.6</v>
       </c>
       <c r="D41" t="n">
-        <v>60.15</v>
+        <v>269.7</v>
       </c>
       <c r="E41" t="n">
-        <v>-8.1</v>
+        <v>-1.1</v>
       </c>
       <c r="F41" t="n">
-        <v>73.01000000000001</v>
+        <v>73.09</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9</v>
+        <v>1.48</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>266.6</v>
+        <v>55.28</v>
       </c>
       <c r="D42" t="n">
-        <v>269.7</v>
+        <v>60.15</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.1</v>
+        <v>-8.1</v>
       </c>
       <c r="F42" t="n">
-        <v>73.09</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>GRMOVER</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>GRM OVERSEAS LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>41.53</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>43.04</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>-3.5</v>
+        <v>-10.7</v>
       </c>
       <c r="F43" t="n">
-        <v>71.79000000000001</v>
+        <v>71.72</v>
       </c>
       <c r="G43" t="n">
-        <v>1.02</v>
+        <v>10.87</v>
       </c>
       <c r="H43" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GRM OVERSEAS LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>85.29000000000001</v>
+        <v>173.3</v>
       </c>
       <c r="D44" t="n">
-        <v>95.54000000000001</v>
+        <v>173.91</v>
       </c>
       <c r="E44" t="n">
-        <v>-10.7</v>
+        <v>-0.4</v>
       </c>
       <c r="F44" t="n">
-        <v>71.72</v>
+        <v>65.64</v>
       </c>
       <c r="G44" t="n">
-        <v>10.87</v>
+        <v>2.61</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>MBEL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>M &amp; B Engineering Limited</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>173.3</v>
+        <v>265.6</v>
       </c>
       <c r="D45" t="n">
-        <v>173.91</v>
+        <v>292.28</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.4</v>
+        <v>-9.1</v>
       </c>
       <c r="F45" t="n">
-        <v>65.64</v>
+        <v>70.45</v>
       </c>
       <c r="G45" t="n">
-        <v>2.61</v>
+        <v>1.29</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MBEL</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>M &amp; B Engineering Limited</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>265.6</v>
+        <v>28.15</v>
       </c>
       <c r="D46" t="n">
-        <v>292.28</v>
+        <v>34.54</v>
       </c>
       <c r="E46" t="n">
-        <v>-9.1</v>
+        <v>-18.5</v>
       </c>
       <c r="F46" t="n">
-        <v>70.45</v>
+        <v>61.81</v>
       </c>
       <c r="G46" t="n">
-        <v>1.29</v>
+        <v>0.88</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>28.15</v>
+        <v>66.19</v>
       </c>
       <c r="D47" t="n">
-        <v>34.54</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>-18.5</v>
+        <v>3.4</v>
       </c>
       <c r="F47" t="n">
-        <v>61.81</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>0.88</v>
+        <v>0.31</v>
       </c>
       <c r="H47" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>66.19</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>64.04000000000001</v>
+        <v>100.33</v>
       </c>
       <c r="E48" t="n">
-        <v>3.4</v>
+        <v>-15.4</v>
       </c>
       <c r="F48" t="n">
-        <v>64.29000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="G48" t="n">
-        <v>0.31</v>
+        <v>0.63</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I48" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>WCIL</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="D49" t="n">
-        <v>100.33</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-15.4</v>
-      </c>
-      <c r="F49" t="n">
-        <v>71.89</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H49" t="n">
-        <v>5</v>
-      </c>
-      <c r="I49" t="inlineStr">
         <is>
           <t>30-06-2026</t>
         </is>
@@ -7049,7 +6917,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -7079,7 +6947,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -7089,7 +6957,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -7099,7 +6967,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -7109,7 +6977,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
